--- a/eval/results/evaluation_metrics_by_qid_full150.xlsx
+++ b/eval/results/evaluation_metrics_by_qid_full150.xlsx
@@ -501,25 +501,25 @@
         <v>150</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.86</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9263157894736842</v>
       </c>
       <c r="D2" t="n">
         <v>0.8627450980392157</v>
       </c>
       <c r="E2" t="n">
-        <v>0.888888888888889</v>
+        <v>0.8934010152284264</v>
       </c>
       <c r="F2" t="n">
         <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
         <v>14</v>
@@ -548,19 +548,19 @@
         <v>150</v>
       </c>
       <c r="B3" t="n">
-        <v>0.92</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9215686274509803</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9306930693069307</v>
       </c>
       <c r="F3" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G3" t="n">
         <v>42</v>
@@ -569,7 +569,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -642,19 +642,19 @@
         <v>150</v>
       </c>
       <c r="B5" t="n">
-        <v>0.76</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9125</v>
+        <v>0.9146341463414634</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7156862745098039</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8021978021978022</v>
+        <v>0.8152173913043479</v>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
         <v>41</v>
@@ -663,7 +663,7 @@
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -689,19 +689,19 @@
         <v>150</v>
       </c>
       <c r="B6" t="n">
-        <v>0.82</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9213483146067416</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="D6" t="n">
-        <v>0.803921568627451</v>
+        <v>0.8137254901960784</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8586387434554974</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="F6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" t="n">
         <v>41</v>
@@ -710,7 +710,7 @@
         <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -833,25 +833,25 @@
         <v>0.7666666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.935064935064935</v>
+        <v>0.9135802469135802</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7254901960784313</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8044692737430168</v>
+        <v>0.8087431693989071</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -880,25 +880,25 @@
         <v>0.7466666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>0.75</v>
+        <v>0.7424242424242424</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9607843137254902</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8347826086956521</v>
+        <v>0.8376068376068376</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1253,19 +1253,19 @@
         <v>150</v>
       </c>
       <c r="B18" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.875</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.823529411764706</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" t="n">
         <v>120</v>
@@ -1274,7 +1274,7 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1303,25 +1303,25 @@
         <v>0.7466666666666667</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4098360655737705</v>
+        <v>0.4126984126984127</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5681818181818182</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1488,25 +1488,25 @@
         <v>150</v>
       </c>
       <c r="B23" t="n">
-        <v>0.88</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5405405405405406</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="D23" t="n">
         <v>0.9523809523809523</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.6779661016949152</v>
       </c>
       <c r="F23" t="n">
         <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1676,25 +1676,25 @@
         <v>150</v>
       </c>
       <c r="B27" t="n">
-        <v>0.86</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="D27" t="n">
         <v>0.7142857142857143</v>
       </c>
       <c r="E27" t="n">
-        <v>0.588235294117647</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="F27" t="n">
         <v>15</v>
       </c>
       <c r="G27" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I27" t="n">
         <v>6</v>
@@ -1723,25 +1723,25 @@
         <v>150</v>
       </c>
       <c r="B28" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="D28" t="n">
         <v>0.9047619047619048</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6031746031746031</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="F28" t="n">
         <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
@@ -1770,25 +1770,25 @@
         <v>150</v>
       </c>
       <c r="B29" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="C29" t="n">
-        <v>0.625</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="D29" t="n">
         <v>0.6818181818181818</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="F29" t="n">
         <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
@@ -2193,25 +2193,25 @@
         <v>150</v>
       </c>
       <c r="B38" t="n">
-        <v>0.7</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8591549295774648</v>
+        <v>0.8714285714285714</v>
       </c>
       <c r="D38" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7305389221556885</v>
+        <v>0.7349397590361446</v>
       </c>
       <c r="F38" t="n">
         <v>61</v>
       </c>
       <c r="G38" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
         <v>35</v>
@@ -2240,25 +2240,25 @@
         <v>150</v>
       </c>
       <c r="B39" t="n">
-        <v>0.72</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="D39" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7529411764705882</v>
+        <v>0.7573964497041421</v>
       </c>
       <c r="F39" t="n">
         <v>64</v>
       </c>
       <c r="G39" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I39" t="n">
         <v>32</v>
@@ -2334,25 +2334,25 @@
         <v>150</v>
       </c>
       <c r="B41" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.6866666666666666</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8939393939393939</v>
+        <v>0.855072463768116</v>
       </c>
       <c r="D41" t="n">
         <v>0.6145833333333334</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7283950617283952</v>
+        <v>0.7151515151515152</v>
       </c>
       <c r="F41" t="n">
         <v>59</v>
       </c>
       <c r="G41" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I41" t="n">
         <v>37</v>
@@ -2522,25 +2522,25 @@
         <v>150</v>
       </c>
       <c r="B45" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.68</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.9137931034482759</v>
       </c>
       <c r="D45" t="n">
         <v>0.5520833333333334</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6973684210526316</v>
+        <v>0.6883116883116883</v>
       </c>
       <c r="F45" t="n">
         <v>53</v>
       </c>
       <c r="G45" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I45" t="n">
         <v>43</v>
@@ -2569,25 +2569,25 @@
         <v>150</v>
       </c>
       <c r="B46" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8051948051948052</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="D46" t="n">
         <v>0.6458333333333334</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7167630057803468</v>
+        <v>0.7126436781609194</v>
       </c>
       <c r="F46" t="n">
         <v>62</v>
       </c>
       <c r="G46" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I46" t="n">
         <v>34</v>
@@ -2616,25 +2616,25 @@
         <v>150</v>
       </c>
       <c r="B47" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6266666666666667</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9347826086956522</v>
+        <v>0.9148936170212766</v>
       </c>
       <c r="D47" t="n">
         <v>0.4526315789473684</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6099290780141844</v>
+        <v>0.6056338028169014</v>
       </c>
       <c r="F47" t="n">
         <v>43</v>
       </c>
       <c r="G47" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
         <v>52</v>
@@ -2663,25 +2663,25 @@
         <v>150</v>
       </c>
       <c r="B48" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.7533333333333333</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.9264705882352942</v>
       </c>
       <c r="D48" t="n">
         <v>0.6631578947368421</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7682926829268292</v>
+        <v>0.773006134969325</v>
       </c>
       <c r="F48" t="n">
         <v>63</v>
       </c>
       <c r="G48" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
         <v>32</v>
@@ -2992,25 +2992,25 @@
         <v>150</v>
       </c>
       <c r="B55" t="n">
-        <v>0.6266666666666667</v>
+        <v>0.62</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="D55" t="n">
         <v>0.5473684210526316</v>
       </c>
       <c r="E55" t="n">
-        <v>0.65</v>
+        <v>0.6459627329192547</v>
       </c>
       <c r="F55" t="n">
         <v>52</v>
       </c>
       <c r="G55" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I55" t="n">
         <v>43</v>
@@ -3086,25 +3086,25 @@
         <v>150</v>
       </c>
       <c r="B57" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8939393939393939</v>
+        <v>0.9076923076923077</v>
       </c>
       <c r="D57" t="n">
         <v>0.6781609195402298</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7712418300653594</v>
+        <v>0.7763157894736842</v>
       </c>
       <c r="F57" t="n">
         <v>59</v>
       </c>
       <c r="G57" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I57" t="n">
         <v>28</v>
@@ -3462,28 +3462,28 @@
         <v>150</v>
       </c>
       <c r="B65" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="C65" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F65" t="n">
+        <v>4</v>
+      </c>
+      <c r="G65" t="n">
+        <v>139</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" t="n">
         <v>5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>140</v>
-      </c>
-      <c r="H65" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" t="n">
-        <v>4</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3509,19 +3509,19 @@
         <v>150</v>
       </c>
       <c r="B66" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E66" t="n">
-        <v>0.6153846153846153</v>
+        <v>0.5</v>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
         <v>141</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3791,19 +3791,19 @@
         <v>150</v>
       </c>
       <c r="B72" t="n">
-        <v>0.9266666666666666</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C72" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1538461538461538</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" t="n">
         <v>138</v>
@@ -3812,7 +3812,7 @@
         <v>3</v>
       </c>
       <c r="I72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3838,19 +3838,19 @@
         <v>150</v>
       </c>
       <c r="B73" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.82</v>
       </c>
       <c r="C73" t="n">
-        <v>0.12</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" t="n">
         <v>119</v>
@@ -3859,7 +3859,7 @@
         <v>22</v>
       </c>
       <c r="I73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3885,25 +3885,25 @@
         <v>150</v>
       </c>
       <c r="B74" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5266666666666666</v>
       </c>
       <c r="C74" t="n">
-        <v>0.72</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="D74" t="n">
         <v>0.5242718446601942</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6067415730337079</v>
+        <v>0.6033519553072626</v>
       </c>
       <c r="F74" t="n">
         <v>54</v>
       </c>
       <c r="G74" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H74" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I74" t="n">
         <v>49</v>
@@ -3932,25 +3932,25 @@
         <v>150</v>
       </c>
       <c r="B75" t="n">
-        <v>0.6066666666666667</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7340425531914894</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="D75" t="n">
         <v>0.6699029126213593</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7005076142131981</v>
+        <v>0.7040816326530613</v>
       </c>
       <c r="F75" t="n">
         <v>69</v>
       </c>
       <c r="G75" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H75" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I75" t="n">
         <v>34</v>
@@ -4073,25 +4073,25 @@
         <v>150</v>
       </c>
       <c r="B78" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6533333333333333</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8271604938271605</v>
+        <v>0.8072289156626506</v>
       </c>
       <c r="D78" t="n">
         <v>0.6504854368932039</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7282608695652175</v>
+        <v>0.7204301075268817</v>
       </c>
       <c r="F78" t="n">
         <v>67</v>
       </c>
       <c r="G78" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H78" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I78" t="n">
         <v>36</v>
@@ -4214,25 +4214,25 @@
         <v>150</v>
       </c>
       <c r="B81" t="n">
-        <v>0.5466666666666666</v>
+        <v>0.5533333333333333</v>
       </c>
       <c r="C81" t="n">
-        <v>0.7868852459016393</v>
+        <v>0.8</v>
       </c>
       <c r="D81" t="n">
         <v>0.4660194174757282</v>
       </c>
       <c r="E81" t="n">
-        <v>0.5853658536585367</v>
+        <v>0.588957055214724</v>
       </c>
       <c r="F81" t="n">
         <v>48</v>
       </c>
       <c r="G81" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H81" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I81" t="n">
         <v>55</v>
@@ -4261,25 +4261,25 @@
         <v>150</v>
       </c>
       <c r="B82" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="C82" t="n">
-        <v>0.801980198019802</v>
+        <v>0.7788461538461539</v>
       </c>
       <c r="D82" t="n">
         <v>0.7864077669902912</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7941176470588236</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="F82" t="n">
         <v>81</v>
       </c>
       <c r="G82" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H82" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I82" t="n">
         <v>22</v>
@@ -4355,25 +4355,25 @@
         <v>150</v>
       </c>
       <c r="B84" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="C84" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8813559322033898</v>
       </c>
       <c r="D84" t="n">
         <v>0.6753246753246753</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7482014388489209</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="F84" t="n">
         <v>52</v>
       </c>
       <c r="G84" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I84" t="n">
         <v>25</v>
@@ -4496,25 +4496,25 @@
         <v>150</v>
       </c>
       <c r="B87" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.74</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.88</v>
       </c>
       <c r="D87" t="n">
         <v>0.5714285714285714</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6984126984126985</v>
+        <v>0.6929133858267715</v>
       </c>
       <c r="F87" t="n">
         <v>44</v>
       </c>
       <c r="G87" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I87" t="n">
         <v>33</v>
@@ -4684,25 +4684,25 @@
         <v>150</v>
       </c>
       <c r="B91" t="n">
-        <v>0.72</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.8113207547169812</v>
       </c>
       <c r="D91" t="n">
         <v>0.5584415584415584</v>
       </c>
       <c r="E91" t="n">
-        <v>0.671875</v>
+        <v>0.6615384615384615</v>
       </c>
       <c r="F91" t="n">
         <v>43</v>
       </c>
       <c r="G91" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I91" t="n">
         <v>34</v>
@@ -4778,19 +4778,19 @@
         <v>150</v>
       </c>
       <c r="B93" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9516129032258065</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="D93" t="n">
-        <v>0.5959595959595959</v>
+        <v>0.6262626262626263</v>
       </c>
       <c r="E93" t="n">
-        <v>0.732919254658385</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="F93" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G93" t="n">
         <v>48</v>
@@ -4799,7 +4799,7 @@
         <v>3</v>
       </c>
       <c r="I93" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -5154,25 +5154,25 @@
         <v>150</v>
       </c>
       <c r="B101" t="n">
-        <v>0.78</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="C101" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="D101" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="E101" t="n">
-        <v>0.6292134831460674</v>
+        <v>0.6363636363636365</v>
       </c>
       <c r="F101" t="n">
         <v>28</v>
       </c>
       <c r="G101" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H101" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I101" t="n">
         <v>14</v>
@@ -5201,25 +5201,25 @@
         <v>150</v>
       </c>
       <c r="B102" t="n">
-        <v>0.82</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6229508196721312</v>
+        <v>0.6440677966101694</v>
       </c>
       <c r="D102" t="n">
         <v>0.9047619047619048</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7378640776699029</v>
+        <v>0.7524752475247525</v>
       </c>
       <c r="F102" t="n">
         <v>38</v>
       </c>
       <c r="G102" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H102" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I102" t="n">
         <v>4</v>
@@ -5483,25 +5483,25 @@
         <v>150</v>
       </c>
       <c r="B108" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="C108" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D108" t="n">
         <v>0.6190476190476191</v>
       </c>
       <c r="E108" t="n">
-        <v>0.6500000000000001</v>
+        <v>0.6419753086419754</v>
       </c>
       <c r="F108" t="n">
         <v>26</v>
       </c>
       <c r="G108" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I108" t="n">
         <v>16</v>
@@ -5530,25 +5530,25 @@
         <v>150</v>
       </c>
       <c r="B109" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4864864864864865</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="D109" t="n">
         <v>0.8571428571428571</v>
       </c>
       <c r="E109" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.6</v>
       </c>
       <c r="F109" t="n">
         <v>36</v>
       </c>
       <c r="G109" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H109" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I109" t="n">
         <v>6</v>
@@ -5765,25 +5765,25 @@
         <v>150</v>
       </c>
       <c r="B114" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="D114" t="n">
         <v>0.8125</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.742857142857143</v>
       </c>
       <c r="F114" t="n">
         <v>13</v>
       </c>
       <c r="G114" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I114" t="n">
         <v>3</v>
@@ -5953,25 +5953,25 @@
         <v>150</v>
       </c>
       <c r="B118" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="C118" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5172413793103449</v>
       </c>
       <c r="D118" t="n">
         <v>0.9375</v>
       </c>
       <c r="E118" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F118" t="n">
         <v>15</v>
       </c>
       <c r="G118" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H118" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -6000,25 +6000,25 @@
         <v>150</v>
       </c>
       <c r="B119" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C119" t="n">
-        <v>0.7068965517241379</v>
+        <v>0.7454545454545455</v>
       </c>
       <c r="D119" t="n">
         <v>0.7068965517241379</v>
       </c>
       <c r="E119" t="n">
-        <v>0.7068965517241379</v>
+        <v>0.7256637168141592</v>
       </c>
       <c r="F119" t="n">
         <v>41</v>
       </c>
       <c r="G119" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H119" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I119" t="n">
         <v>17</v>
@@ -6050,25 +6050,25 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C120" t="n">
-        <v>0.72</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.9137931034482759</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8120300751879699</v>
+        <v>0.8091603053435115</v>
       </c>
       <c r="F120" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G120" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H120" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -6329,25 +6329,25 @@
         <v>150</v>
       </c>
       <c r="B126" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C126" t="n">
-        <v>0.75</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="D126" t="n">
         <v>0.6724137931034483</v>
       </c>
       <c r="E126" t="n">
-        <v>0.709090909090909</v>
+        <v>0.6964285714285714</v>
       </c>
       <c r="F126" t="n">
         <v>39</v>
       </c>
       <c r="G126" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H126" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I126" t="n">
         <v>19</v>
@@ -6376,28 +6376,28 @@
         <v>150</v>
       </c>
       <c r="B127" t="n">
-        <v>0.62</v>
+        <v>0.6066666666666667</v>
       </c>
       <c r="C127" t="n">
-        <v>0.504950495049505</v>
+        <v>0.4952380952380953</v>
       </c>
       <c r="D127" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="E127" t="n">
-        <v>0.6415094339622641</v>
+        <v>0.6380368098159509</v>
       </c>
       <c r="F127" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G127" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H127" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6470,25 +6470,25 @@
         <v>150</v>
       </c>
       <c r="B129" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="C129" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D129" t="n">
         <v>0.5970149253731343</v>
       </c>
       <c r="E129" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6504065040650405</v>
       </c>
       <c r="F129" t="n">
         <v>40</v>
       </c>
       <c r="G129" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H129" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I129" t="n">
         <v>27</v>
@@ -6564,25 +6564,25 @@
         <v>150</v>
       </c>
       <c r="B131" t="n">
-        <v>0.4066666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="C131" t="n">
-        <v>0.392156862745098</v>
+        <v>0.3883495145631068</v>
       </c>
       <c r="D131" t="n">
         <v>0.5970149253731343</v>
       </c>
       <c r="E131" t="n">
-        <v>0.4733727810650887</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="F131" t="n">
         <v>40</v>
       </c>
       <c r="G131" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H131" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I131" t="n">
         <v>27</v>
@@ -6611,25 +6611,25 @@
         <v>150</v>
       </c>
       <c r="B132" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.62</v>
       </c>
       <c r="C132" t="n">
-        <v>0.84</v>
+        <v>0.65625</v>
       </c>
       <c r="D132" t="n">
         <v>0.3134328358208955</v>
       </c>
       <c r="E132" t="n">
-        <v>0.4565217391304348</v>
+        <v>0.4242424242424243</v>
       </c>
       <c r="F132" t="n">
         <v>21</v>
       </c>
       <c r="G132" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H132" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I132" t="n">
         <v>46</v>
@@ -6799,25 +6799,25 @@
         <v>150</v>
       </c>
       <c r="B136" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5266666666666666</v>
       </c>
       <c r="C136" t="n">
-        <v>0.4805194805194805</v>
+        <v>0.4743589743589743</v>
       </c>
       <c r="D136" t="n">
         <v>0.5522388059701493</v>
       </c>
       <c r="E136" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.5103448275862068</v>
       </c>
       <c r="F136" t="n">
         <v>37</v>
       </c>
       <c r="G136" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H136" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I136" t="n">
         <v>30</v>
@@ -6849,25 +6849,25 @@
         <v>0.6066666666666667</v>
       </c>
       <c r="C137" t="n">
-        <v>0.5102040816326531</v>
+        <v>0.5098039215686274</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="E137" t="n">
-        <v>0.4587155963302753</v>
+        <v>0.4684684684684685</v>
       </c>
       <c r="F137" t="n">
+        <v>26</v>
+      </c>
+      <c r="G137" t="n">
+        <v>65</v>
+      </c>
+      <c r="H137" t="n">
         <v>25</v>
       </c>
-      <c r="G137" t="n">
-        <v>66</v>
-      </c>
-      <c r="H137" t="n">
-        <v>24</v>
-      </c>
       <c r="I137" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -6893,25 +6893,25 @@
         <v>150</v>
       </c>
       <c r="B138" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C138" t="n">
-        <v>0.7346938775510204</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="D138" t="n">
         <v>0.6</v>
       </c>
       <c r="E138" t="n">
-        <v>0.6605504587155964</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="F138" t="n">
         <v>36</v>
       </c>
       <c r="G138" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H138" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I138" t="n">
         <v>24</v>
@@ -6987,25 +6987,25 @@
         <v>150</v>
       </c>
       <c r="B140" t="n">
-        <v>0.3466666666666667</v>
+        <v>0.34</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2934782608695652</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="D140" t="n">
         <v>0.45</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3552631578947368</v>
+        <v>0.3529411764705882</v>
       </c>
       <c r="F140" t="n">
         <v>27</v>
       </c>
       <c r="G140" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H140" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I140" t="n">
         <v>33</v>
@@ -7225,25 +7225,25 @@
         <v>0.52</v>
       </c>
       <c r="C145" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D145" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.35</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3571428571428571</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="F145" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G145" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H145" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I145" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7350,25 +7350,25 @@
         <v>150</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.86</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9263157894736842</v>
       </c>
       <c r="D2" t="n">
         <v>0.8627450980392157</v>
       </c>
       <c r="E2" t="n">
-        <v>0.888888888888889</v>
+        <v>0.8934010152284264</v>
       </c>
       <c r="F2" t="n">
         <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
         <v>14</v>
@@ -7397,19 +7397,19 @@
         <v>150</v>
       </c>
       <c r="B3" t="n">
-        <v>0.92</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9215686274509803</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9306930693069307</v>
       </c>
       <c r="F3" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G3" t="n">
         <v>42</v>
@@ -7418,7 +7418,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -7491,19 +7491,19 @@
         <v>150</v>
       </c>
       <c r="B5" t="n">
-        <v>0.76</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9125</v>
+        <v>0.9146341463414634</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7156862745098039</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8021978021978022</v>
+        <v>0.8152173913043479</v>
       </c>
       <c r="F5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
         <v>41</v>
@@ -7512,7 +7512,7 @@
         <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -7538,19 +7538,19 @@
         <v>150</v>
       </c>
       <c r="B6" t="n">
-        <v>0.82</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9213483146067416</v>
+        <v>0.9222222222222223</v>
       </c>
       <c r="D6" t="n">
-        <v>0.803921568627451</v>
+        <v>0.8137254901960784</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8586387434554974</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="F6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" t="n">
         <v>41</v>
@@ -7559,7 +7559,7 @@
         <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -7682,25 +7682,25 @@
         <v>0.7666666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.935064935064935</v>
+        <v>0.9135802469135802</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7254901960784313</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8044692737430168</v>
+        <v>0.8087431693989071</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -7729,25 +7729,25 @@
         <v>0.7466666666666667</v>
       </c>
       <c r="C10" t="n">
-        <v>0.75</v>
+        <v>0.7424242424242424</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9607843137254902</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8347826086956521</v>
+        <v>0.8376068376068376</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -8102,19 +8102,19 @@
         <v>150</v>
       </c>
       <c r="B18" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.875</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.823529411764706</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" t="n">
         <v>120</v>
@@ -8123,7 +8123,7 @@
         <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -8152,25 +8152,25 @@
         <v>0.7466666666666667</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4098360655737705</v>
+        <v>0.4126984126984127</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5681818181818182</v>
+        <v>0.5777777777777777</v>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -8337,25 +8337,25 @@
         <v>150</v>
       </c>
       <c r="B23" t="n">
-        <v>0.88</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5405405405405406</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="D23" t="n">
         <v>0.9523809523809523</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.6779661016949152</v>
       </c>
       <c r="F23" t="n">
         <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -8525,25 +8525,25 @@
         <v>150</v>
       </c>
       <c r="B27" t="n">
-        <v>0.86</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="C27" t="n">
-        <v>0.5</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="D27" t="n">
         <v>0.7142857142857143</v>
       </c>
       <c r="E27" t="n">
-        <v>0.588235294117647</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="F27" t="n">
         <v>15</v>
       </c>
       <c r="G27" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I27" t="n">
         <v>6</v>
@@ -8572,25 +8572,25 @@
         <v>150</v>
       </c>
       <c r="B28" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.4222222222222222</v>
       </c>
       <c r="D28" t="n">
         <v>0.9047619047619048</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6031746031746031</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="F28" t="n">
         <v>19</v>
       </c>
       <c r="G28" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
@@ -8619,25 +8619,25 @@
         <v>150</v>
       </c>
       <c r="B29" t="n">
-        <v>0.8933333333333333</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="C29" t="n">
-        <v>0.625</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="D29" t="n">
         <v>0.6818181818181818</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="F29" t="n">
         <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
@@ -9042,25 +9042,25 @@
         <v>150</v>
       </c>
       <c r="B38" t="n">
-        <v>0.7</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8591549295774648</v>
+        <v>0.8714285714285714</v>
       </c>
       <c r="D38" t="n">
         <v>0.6354166666666666</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7305389221556885</v>
+        <v>0.7349397590361446</v>
       </c>
       <c r="F38" t="n">
         <v>61</v>
       </c>
       <c r="G38" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
         <v>35</v>
@@ -9089,25 +9089,25 @@
         <v>150</v>
       </c>
       <c r="B39" t="n">
-        <v>0.72</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.8767123287671232</v>
       </c>
       <c r="D39" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7529411764705882</v>
+        <v>0.7573964497041421</v>
       </c>
       <c r="F39" t="n">
         <v>64</v>
       </c>
       <c r="G39" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I39" t="n">
         <v>32</v>
@@ -9183,25 +9183,25 @@
         <v>150</v>
       </c>
       <c r="B41" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.6866666666666666</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8939393939393939</v>
+        <v>0.855072463768116</v>
       </c>
       <c r="D41" t="n">
         <v>0.6145833333333334</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7283950617283952</v>
+        <v>0.7151515151515152</v>
       </c>
       <c r="F41" t="n">
         <v>59</v>
       </c>
       <c r="G41" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I41" t="n">
         <v>37</v>
@@ -9371,25 +9371,25 @@
         <v>150</v>
       </c>
       <c r="B45" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.68</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.9137931034482759</v>
       </c>
       <c r="D45" t="n">
         <v>0.5520833333333334</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6973684210526316</v>
+        <v>0.6883116883116883</v>
       </c>
       <c r="F45" t="n">
         <v>53</v>
       </c>
       <c r="G45" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I45" t="n">
         <v>43</v>
@@ -9418,25 +9418,25 @@
         <v>150</v>
       </c>
       <c r="B46" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8051948051948052</v>
+        <v>0.7948717948717948</v>
       </c>
       <c r="D46" t="n">
         <v>0.6458333333333334</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7167630057803468</v>
+        <v>0.7126436781609194</v>
       </c>
       <c r="F46" t="n">
         <v>62</v>
       </c>
       <c r="G46" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I46" t="n">
         <v>34</v>
@@ -9465,25 +9465,25 @@
         <v>150</v>
       </c>
       <c r="B47" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.6266666666666667</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9347826086956522</v>
+        <v>0.9148936170212766</v>
       </c>
       <c r="D47" t="n">
         <v>0.4526315789473684</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6099290780141844</v>
+        <v>0.6056338028169014</v>
       </c>
       <c r="F47" t="n">
         <v>43</v>
       </c>
       <c r="G47" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
         <v>52</v>
@@ -9512,25 +9512,25 @@
         <v>150</v>
       </c>
       <c r="B48" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.7533333333333333</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.9264705882352942</v>
       </c>
       <c r="D48" t="n">
         <v>0.6631578947368421</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7682926829268292</v>
+        <v>0.773006134969325</v>
       </c>
       <c r="F48" t="n">
         <v>63</v>
       </c>
       <c r="G48" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
         <v>32</v>
@@ -9841,25 +9841,25 @@
         <v>150</v>
       </c>
       <c r="B55" t="n">
-        <v>0.6266666666666667</v>
+        <v>0.62</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="D55" t="n">
         <v>0.5473684210526316</v>
       </c>
       <c r="E55" t="n">
-        <v>0.65</v>
+        <v>0.6459627329192547</v>
       </c>
       <c r="F55" t="n">
         <v>52</v>
       </c>
       <c r="G55" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H55" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I55" t="n">
         <v>43</v>
@@ -9935,25 +9935,25 @@
         <v>150</v>
       </c>
       <c r="B57" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8939393939393939</v>
+        <v>0.9076923076923077</v>
       </c>
       <c r="D57" t="n">
         <v>0.6781609195402298</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7712418300653594</v>
+        <v>0.7763157894736842</v>
       </c>
       <c r="F57" t="n">
         <v>59</v>
       </c>
       <c r="G57" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I57" t="n">
         <v>28</v>
@@ -10311,28 +10311,28 @@
         <v>150</v>
       </c>
       <c r="B65" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="C65" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D65" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E65" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F65" t="n">
+        <v>4</v>
+      </c>
+      <c r="G65" t="n">
+        <v>139</v>
+      </c>
+      <c r="H65" t="n">
+        <v>2</v>
+      </c>
+      <c r="I65" t="n">
         <v>5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>140</v>
-      </c>
-      <c r="H65" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" t="n">
-        <v>4</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -10358,19 +10358,19 @@
         <v>150</v>
       </c>
       <c r="B66" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.96</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E66" t="n">
-        <v>0.6153846153846153</v>
+        <v>0.5</v>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
         <v>141</v>
@@ -10379,7 +10379,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -10640,19 +10640,19 @@
         <v>150</v>
       </c>
       <c r="B72" t="n">
-        <v>0.9266666666666666</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C72" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1538461538461538</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" t="n">
         <v>138</v>
@@ -10661,7 +10661,7 @@
         <v>3</v>
       </c>
       <c r="I72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -10687,19 +10687,19 @@
         <v>150</v>
       </c>
       <c r="B73" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.82</v>
       </c>
       <c r="C73" t="n">
-        <v>0.12</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="D73" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G73" t="n">
         <v>119</v>
@@ -10708,7 +10708,7 @@
         <v>22</v>
       </c>
       <c r="I73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -10734,25 +10734,25 @@
         <v>150</v>
       </c>
       <c r="B74" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5266666666666666</v>
       </c>
       <c r="C74" t="n">
-        <v>0.72</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="D74" t="n">
         <v>0.5242718446601942</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6067415730337079</v>
+        <v>0.6033519553072626</v>
       </c>
       <c r="F74" t="n">
         <v>54</v>
       </c>
       <c r="G74" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H74" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I74" t="n">
         <v>49</v>
@@ -10781,25 +10781,25 @@
         <v>150</v>
       </c>
       <c r="B75" t="n">
-        <v>0.6066666666666667</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7340425531914894</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="D75" t="n">
         <v>0.6699029126213593</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7005076142131981</v>
+        <v>0.7040816326530613</v>
       </c>
       <c r="F75" t="n">
         <v>69</v>
       </c>
       <c r="G75" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H75" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I75" t="n">
         <v>34</v>
@@ -10922,25 +10922,25 @@
         <v>150</v>
       </c>
       <c r="B78" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6533333333333333</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8271604938271605</v>
+        <v>0.8072289156626506</v>
       </c>
       <c r="D78" t="n">
         <v>0.6504854368932039</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7282608695652175</v>
+        <v>0.7204301075268817</v>
       </c>
       <c r="F78" t="n">
         <v>67</v>
       </c>
       <c r="G78" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H78" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I78" t="n">
         <v>36</v>
@@ -11063,25 +11063,25 @@
         <v>150</v>
       </c>
       <c r="B81" t="n">
-        <v>0.5466666666666666</v>
+        <v>0.5533333333333333</v>
       </c>
       <c r="C81" t="n">
-        <v>0.7868852459016393</v>
+        <v>0.8</v>
       </c>
       <c r="D81" t="n">
         <v>0.4660194174757282</v>
       </c>
       <c r="E81" t="n">
-        <v>0.5853658536585367</v>
+        <v>0.588957055214724</v>
       </c>
       <c r="F81" t="n">
         <v>48</v>
       </c>
       <c r="G81" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H81" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I81" t="n">
         <v>55</v>
@@ -11110,25 +11110,25 @@
         <v>150</v>
       </c>
       <c r="B82" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="C82" t="n">
-        <v>0.801980198019802</v>
+        <v>0.7788461538461539</v>
       </c>
       <c r="D82" t="n">
         <v>0.7864077669902912</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7941176470588236</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="F82" t="n">
         <v>81</v>
       </c>
       <c r="G82" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H82" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I82" t="n">
         <v>22</v>
@@ -11204,25 +11204,25 @@
         <v>150</v>
       </c>
       <c r="B84" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="C84" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8813559322033898</v>
       </c>
       <c r="D84" t="n">
         <v>0.6753246753246753</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7482014388489209</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="F84" t="n">
         <v>52</v>
       </c>
       <c r="G84" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I84" t="n">
         <v>25</v>
@@ -11345,25 +11345,25 @@
         <v>150</v>
       </c>
       <c r="B87" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.74</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8979591836734694</v>
+        <v>0.88</v>
       </c>
       <c r="D87" t="n">
         <v>0.5714285714285714</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6984126984126985</v>
+        <v>0.6929133858267715</v>
       </c>
       <c r="F87" t="n">
         <v>44</v>
       </c>
       <c r="G87" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H87" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I87" t="n">
         <v>33</v>
@@ -11533,25 +11533,25 @@
         <v>150</v>
       </c>
       <c r="B91" t="n">
-        <v>0.72</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8431372549019608</v>
+        <v>0.8113207547169812</v>
       </c>
       <c r="D91" t="n">
         <v>0.5584415584415584</v>
       </c>
       <c r="E91" t="n">
-        <v>0.671875</v>
+        <v>0.6615384615384615</v>
       </c>
       <c r="F91" t="n">
         <v>43</v>
       </c>
       <c r="G91" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I91" t="n">
         <v>34</v>
@@ -11627,19 +11627,19 @@
         <v>150</v>
       </c>
       <c r="B93" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9516129032258065</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="D93" t="n">
-        <v>0.5959595959595959</v>
+        <v>0.6262626262626263</v>
       </c>
       <c r="E93" t="n">
-        <v>0.732919254658385</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="F93" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G93" t="n">
         <v>48</v>
@@ -11648,7 +11648,7 @@
         <v>3</v>
       </c>
       <c r="I93" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -12003,25 +12003,25 @@
         <v>150</v>
       </c>
       <c r="B101" t="n">
-        <v>0.78</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="C101" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="D101" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="E101" t="n">
-        <v>0.6292134831460674</v>
+        <v>0.6363636363636365</v>
       </c>
       <c r="F101" t="n">
         <v>28</v>
       </c>
       <c r="G101" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H101" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I101" t="n">
         <v>14</v>
@@ -12050,25 +12050,25 @@
         <v>150</v>
       </c>
       <c r="B102" t="n">
-        <v>0.82</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6229508196721312</v>
+        <v>0.6440677966101694</v>
       </c>
       <c r="D102" t="n">
         <v>0.9047619047619048</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7378640776699029</v>
+        <v>0.7524752475247525</v>
       </c>
       <c r="F102" t="n">
         <v>38</v>
       </c>
       <c r="G102" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H102" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I102" t="n">
         <v>4</v>
@@ -12332,25 +12332,25 @@
         <v>150</v>
       </c>
       <c r="B108" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="C108" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D108" t="n">
         <v>0.6190476190476191</v>
       </c>
       <c r="E108" t="n">
-        <v>0.6500000000000001</v>
+        <v>0.6419753086419754</v>
       </c>
       <c r="F108" t="n">
         <v>26</v>
       </c>
       <c r="G108" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I108" t="n">
         <v>16</v>
@@ -12379,25 +12379,25 @@
         <v>150</v>
       </c>
       <c r="B109" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4864864864864865</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="D109" t="n">
         <v>0.8571428571428571</v>
       </c>
       <c r="E109" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.6</v>
       </c>
       <c r="F109" t="n">
         <v>36</v>
       </c>
       <c r="G109" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H109" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I109" t="n">
         <v>6</v>
@@ -12614,25 +12614,25 @@
         <v>150</v>
       </c>
       <c r="B114" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="D114" t="n">
         <v>0.8125</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.742857142857143</v>
       </c>
       <c r="F114" t="n">
         <v>13</v>
       </c>
       <c r="G114" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I114" t="n">
         <v>3</v>
@@ -12802,25 +12802,25 @@
         <v>150</v>
       </c>
       <c r="B118" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9</v>
       </c>
       <c r="C118" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5172413793103449</v>
       </c>
       <c r="D118" t="n">
         <v>0.9375</v>
       </c>
       <c r="E118" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F118" t="n">
         <v>15</v>
       </c>
       <c r="G118" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H118" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I118" t="n">
         <v>1</v>
@@ -12849,25 +12849,25 @@
         <v>150</v>
       </c>
       <c r="B119" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C119" t="n">
-        <v>0.7068965517241379</v>
+        <v>0.7454545454545455</v>
       </c>
       <c r="D119" t="n">
         <v>0.7068965517241379</v>
       </c>
       <c r="E119" t="n">
-        <v>0.7068965517241379</v>
+        <v>0.7256637168141592</v>
       </c>
       <c r="F119" t="n">
         <v>41</v>
       </c>
       <c r="G119" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H119" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I119" t="n">
         <v>17</v>
@@ -12899,25 +12899,25 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="C120" t="n">
-        <v>0.72</v>
+        <v>0.726027397260274</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.9137931034482759</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8120300751879699</v>
+        <v>0.8091603053435115</v>
       </c>
       <c r="F120" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G120" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H120" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I120" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -13178,25 +13178,25 @@
         <v>150</v>
       </c>
       <c r="B126" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C126" t="n">
-        <v>0.75</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="D126" t="n">
         <v>0.6724137931034483</v>
       </c>
       <c r="E126" t="n">
-        <v>0.709090909090909</v>
+        <v>0.6964285714285714</v>
       </c>
       <c r="F126" t="n">
         <v>39</v>
       </c>
       <c r="G126" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H126" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I126" t="n">
         <v>19</v>
@@ -13225,28 +13225,28 @@
         <v>150</v>
       </c>
       <c r="B127" t="n">
-        <v>0.62</v>
+        <v>0.6066666666666667</v>
       </c>
       <c r="C127" t="n">
-        <v>0.504950495049505</v>
+        <v>0.4952380952380953</v>
       </c>
       <c r="D127" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="E127" t="n">
-        <v>0.6415094339622641</v>
+        <v>0.6380368098159509</v>
       </c>
       <c r="F127" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G127" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H127" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -13319,25 +13319,25 @@
         <v>150</v>
       </c>
       <c r="B129" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="C129" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D129" t="n">
         <v>0.5970149253731343</v>
       </c>
       <c r="E129" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6504065040650405</v>
       </c>
       <c r="F129" t="n">
         <v>40</v>
       </c>
       <c r="G129" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H129" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I129" t="n">
         <v>27</v>
@@ -13413,25 +13413,25 @@
         <v>150</v>
       </c>
       <c r="B131" t="n">
-        <v>0.4066666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="C131" t="n">
-        <v>0.392156862745098</v>
+        <v>0.3883495145631068</v>
       </c>
       <c r="D131" t="n">
         <v>0.5970149253731343</v>
       </c>
       <c r="E131" t="n">
-        <v>0.4733727810650887</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="F131" t="n">
         <v>40</v>
       </c>
       <c r="G131" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H131" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I131" t="n">
         <v>27</v>
@@ -13460,25 +13460,25 @@
         <v>150</v>
       </c>
       <c r="B132" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.62</v>
       </c>
       <c r="C132" t="n">
-        <v>0.84</v>
+        <v>0.65625</v>
       </c>
       <c r="D132" t="n">
         <v>0.3134328358208955</v>
       </c>
       <c r="E132" t="n">
-        <v>0.4565217391304348</v>
+        <v>0.4242424242424243</v>
       </c>
       <c r="F132" t="n">
         <v>21</v>
       </c>
       <c r="G132" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H132" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I132" t="n">
         <v>46</v>
@@ -13648,25 +13648,25 @@
         <v>150</v>
       </c>
       <c r="B136" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5266666666666666</v>
       </c>
       <c r="C136" t="n">
-        <v>0.4805194805194805</v>
+        <v>0.4743589743589743</v>
       </c>
       <c r="D136" t="n">
         <v>0.5522388059701493</v>
       </c>
       <c r="E136" t="n">
-        <v>0.5138888888888888</v>
+        <v>0.5103448275862068</v>
       </c>
       <c r="F136" t="n">
         <v>37</v>
       </c>
       <c r="G136" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H136" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I136" t="n">
         <v>30</v>
@@ -13698,25 +13698,25 @@
         <v>0.6066666666666667</v>
       </c>
       <c r="C137" t="n">
-        <v>0.5102040816326531</v>
+        <v>0.5098039215686274</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="E137" t="n">
-        <v>0.4587155963302753</v>
+        <v>0.4684684684684685</v>
       </c>
       <c r="F137" t="n">
+        <v>26</v>
+      </c>
+      <c r="G137" t="n">
+        <v>65</v>
+      </c>
+      <c r="H137" t="n">
         <v>25</v>
       </c>
-      <c r="G137" t="n">
-        <v>66</v>
-      </c>
-      <c r="H137" t="n">
-        <v>24</v>
-      </c>
       <c r="I137" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -13742,25 +13742,25 @@
         <v>150</v>
       </c>
       <c r="B138" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C138" t="n">
-        <v>0.7346938775510204</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="D138" t="n">
         <v>0.6</v>
       </c>
       <c r="E138" t="n">
-        <v>0.6605504587155964</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="F138" t="n">
         <v>36</v>
       </c>
       <c r="G138" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H138" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I138" t="n">
         <v>24</v>
@@ -13836,25 +13836,25 @@
         <v>150</v>
       </c>
       <c r="B140" t="n">
-        <v>0.3466666666666667</v>
+        <v>0.34</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2934782608695652</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="D140" t="n">
         <v>0.45</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3552631578947368</v>
+        <v>0.3529411764705882</v>
       </c>
       <c r="F140" t="n">
         <v>27</v>
       </c>
       <c r="G140" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H140" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I140" t="n">
         <v>33</v>
@@ -14074,25 +14074,25 @@
         <v>0.52</v>
       </c>
       <c r="C145" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D145" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.35</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3571428571428571</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="F145" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G145" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H145" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I145" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>

--- a/eval/results/evaluation_metrics_by_qid_full150.xlsx
+++ b/eval/results/evaluation_metrics_by_qid_full150.xlsx
@@ -501,25 +501,25 @@
         <v>150</v>
       </c>
       <c r="B2" t="n">
-        <v>0.86</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9263157894736842</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D2" t="n">
         <v>0.8627450980392157</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8934010152284264</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F2" t="n">
         <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>14</v>
@@ -548,19 +548,19 @@
         <v>150</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.92</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9215686274509803</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9306930693069307</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G3" t="n">
         <v>42</v>
@@ -569,7 +569,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -877,19 +877,19 @@
         <v>150</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7424242424242424</v>
+        <v>0.75</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9607843137254902</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8376068376068376</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F10" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G10" t="n">
         <v>14</v>
@@ -898,7 +898,7 @@
         <v>34</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1300,19 +1300,19 @@
         <v>150</v>
       </c>
       <c r="B19" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.7533333333333333</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.421875</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9629629629629629</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.5934065934065934</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>86</v>
@@ -1321,7 +1321,7 @@
         <v>37</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1347,28 +1347,28 @@
         <v>150</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9733333333333334</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8163265306122449</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G20" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1394,25 +1394,25 @@
         <v>150</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7307692307692307</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.962962962962963</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
         <v>122</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
@@ -1444,19 +1444,19 @@
         <v>0.9533333333333334</v>
       </c>
       <c r="C22" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G22" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H22" t="n">
         <v>7</v>
@@ -1488,25 +1488,25 @@
         <v>150</v>
       </c>
       <c r="B23" t="n">
-        <v>0.8733333333333333</v>
+        <v>0.92</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6779661016949152</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
         <v>111</v>
       </c>
       <c r="H23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1535,28 +1535,28 @@
         <v>150</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E24" t="n">
-        <v>0.888888888888889</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="F24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1582,25 +1582,25 @@
         <v>150</v>
       </c>
       <c r="B25" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.8852459016393442</v>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G25" t="n">
         <v>116</v>
       </c>
       <c r="H25" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1629,25 +1629,25 @@
         <v>150</v>
       </c>
       <c r="B26" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7164179104477612</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
         <v>107</v>
       </c>
       <c r="H26" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I26" t="n">
         <v>4</v>
@@ -1676,28 +1676,28 @@
         <v>150</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.86</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.6440677966101694</v>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H27" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1723,28 +1723,28 @@
         <v>150</v>
       </c>
       <c r="B28" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.5869565217391305</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5757575757575758</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G28" t="n">
         <v>103</v>
       </c>
       <c r="H28" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1770,28 +1770,28 @@
         <v>150</v>
       </c>
       <c r="B29" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.7</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1817,19 +1817,19 @@
         <v>150</v>
       </c>
       <c r="B30" t="n">
-        <v>0.9266666666666666</v>
+        <v>0.96</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
         <v>124</v>
@@ -1838,7 +1838,7 @@
         <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1864,19 +1864,19 @@
         <v>150</v>
       </c>
       <c r="B31" t="n">
-        <v>0.9933333333333333</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9777777777777777</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="F31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G31" t="n">
         <v>127</v>
@@ -1885,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1911,19 +1911,19 @@
         <v>150</v>
       </c>
       <c r="B32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.9268292682926829</v>
       </c>
       <c r="F32" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G32" t="n">
         <v>128</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1958,19 +1958,19 @@
         <v>150</v>
       </c>
       <c r="B33" t="n">
-        <v>0.9533333333333334</v>
+        <v>0.98</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.9268292682926829</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G33" t="n">
         <v>128</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2005,19 +2005,19 @@
         <v>150</v>
       </c>
       <c r="B34" t="n">
-        <v>0.9533333333333334</v>
+        <v>0.9933333333333333</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.9767441860465117</v>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G34" t="n">
         <v>128</v>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2052,19 +2052,19 @@
         <v>150</v>
       </c>
       <c r="B35" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.9268292682926829</v>
       </c>
       <c r="F35" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G35" t="n">
         <v>128</v>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2099,19 +2099,19 @@
         <v>150</v>
       </c>
       <c r="B36" t="n">
-        <v>0.9266666666666666</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G36" t="n">
         <v>128</v>
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2146,19 +2146,19 @@
         <v>150</v>
       </c>
       <c r="B37" t="n">
-        <v>0.92</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.84</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.8936170212765958</v>
       </c>
       <c r="F37" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G37" t="n">
         <v>124</v>
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="I37" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2193,28 +2193,28 @@
         <v>150</v>
       </c>
       <c r="B38" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8714285714285714</v>
+        <v>0.9375</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.7425742574257426</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7349397590361446</v>
+        <v>0.8287292817679558</v>
       </c>
       <c r="F38" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="G38" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I38" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2240,28 +2240,28 @@
         <v>150</v>
       </c>
       <c r="B39" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8767123287671232</v>
+        <v>0.95</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7524752475247525</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7573964497041421</v>
+        <v>0.8397790055248618</v>
       </c>
       <c r="F39" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G39" t="n">
         <v>45</v>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2287,28 +2287,28 @@
         <v>150</v>
       </c>
       <c r="B40" t="n">
-        <v>0.86</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9518072289156626</v>
+        <v>0.9294117647058824</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.7821782178217822</v>
       </c>
       <c r="E40" t="n">
-        <v>0.88268156424581</v>
+        <v>0.8494623655913979</v>
       </c>
       <c r="F40" t="n">
         <v>79</v>
       </c>
       <c r="G40" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2334,28 +2334,28 @@
         <v>150</v>
       </c>
       <c r="B41" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.8</v>
       </c>
       <c r="C41" t="n">
-        <v>0.855072463768116</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.7425742574257426</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7151515151515152</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F41" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G41" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I41" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2381,28 +2381,28 @@
         <v>150</v>
       </c>
       <c r="B42" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.78</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8983050847457628</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.6732673267326733</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6838709677419356</v>
+        <v>0.8047337278106509</v>
       </c>
       <c r="F42" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="G42" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2428,28 +2428,28 @@
         <v>150</v>
       </c>
       <c r="B43" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8767123287671232</v>
+        <v>0.9634146341463414</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7821782178217822</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7573964497041421</v>
+        <v>0.8633879781420765</v>
       </c>
       <c r="F43" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="G43" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2475,28 +2475,28 @@
         <v>150</v>
       </c>
       <c r="B44" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8688524590163934</v>
+        <v>0.9402985074626866</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.6237623762376238</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6751592356687898</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G44" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2522,28 +2522,28 @@
         <v>150</v>
       </c>
       <c r="B45" t="n">
-        <v>0.68</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9137931034482759</v>
+        <v>0.953125</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.6039603960396039</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6883116883116883</v>
+        <v>0.7393939393939394</v>
       </c>
       <c r="F45" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G45" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2569,28 +2569,28 @@
         <v>150</v>
       </c>
       <c r="B46" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.851063829787234</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.7920792079207921</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7126436781609194</v>
+        <v>0.8205128205128204</v>
       </c>
       <c r="F46" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G46" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H46" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I46" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2616,28 +2616,28 @@
         <v>150</v>
       </c>
       <c r="B47" t="n">
-        <v>0.6266666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9148936170212766</v>
+        <v>0.9242424242424242</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4526315789473684</v>
+        <v>0.6630434782608695</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6056338028169014</v>
+        <v>0.7721518987341771</v>
       </c>
       <c r="F47" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="G47" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2663,28 +2663,28 @@
         <v>150</v>
       </c>
       <c r="B48" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.88</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9264705882352942</v>
+        <v>0.9204545454545454</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6631578947368421</v>
+        <v>0.8804347826086957</v>
       </c>
       <c r="E48" t="n">
-        <v>0.773006134969325</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="G48" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I48" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2710,28 +2710,28 @@
         <v>150</v>
       </c>
       <c r="B49" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8210526315789474</v>
+        <v>0.83</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8210526315789474</v>
+        <v>0.9021739130434783</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8210526315789475</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="F49" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G49" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H49" t="n">
         <v>17</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2757,28 +2757,28 @@
         <v>150</v>
       </c>
       <c r="B50" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5368421052631579</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6496815286624203</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G50" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I50" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2804,28 +2804,28 @@
         <v>150</v>
       </c>
       <c r="B51" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.84</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9482758620689655</v>
+        <v>0.9594594594594594</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.7717391304347826</v>
       </c>
       <c r="E51" t="n">
-        <v>0.7189542483660131</v>
+        <v>0.855421686746988</v>
       </c>
       <c r="F51" t="n">
+        <v>71</v>
+      </c>
+      <c r="G51" t="n">
         <v>55</v>
-      </c>
-      <c r="G51" t="n">
-        <v>52</v>
       </c>
       <c r="H51" t="n">
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2851,28 +2851,28 @@
         <v>150</v>
       </c>
       <c r="B52" t="n">
-        <v>0.74</v>
+        <v>0.8866666666666667</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9516129032258065</v>
+        <v>0.9746835443037974</v>
       </c>
       <c r="D52" t="n">
-        <v>0.6210526315789474</v>
+        <v>0.8369565217391305</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7515923566878981</v>
+        <v>0.9005847953216375</v>
       </c>
       <c r="F52" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="G52" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2898,28 +2898,28 @@
         <v>150</v>
       </c>
       <c r="B53" t="n">
-        <v>0.5933333333333334</v>
+        <v>0.68</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9722222222222222</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5343511450381679</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="F53" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G53" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2945,28 +2945,28 @@
         <v>150</v>
       </c>
       <c r="B54" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8936170212765957</v>
+        <v>0.9322033898305084</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4421052631578947</v>
+        <v>0.5978260869565217</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5915492957746478</v>
+        <v>0.728476821192053</v>
       </c>
       <c r="F54" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G54" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I54" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2992,28 +2992,28 @@
         <v>150</v>
       </c>
       <c r="B55" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.8470588235294118</v>
       </c>
       <c r="D55" t="n">
-        <v>0.5473684210526316</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="E55" t="n">
-        <v>0.6459627329192547</v>
+        <v>0.8135593220338984</v>
       </c>
       <c r="F55" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G55" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I55" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3039,28 +3039,28 @@
         <v>150</v>
       </c>
       <c r="B56" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8909090909090909</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="D56" t="n">
-        <v>0.5632183908045977</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6901408450704224</v>
+        <v>0.8354430379746836</v>
       </c>
       <c r="F56" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G56" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I56" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3086,28 +3086,28 @@
         <v>150</v>
       </c>
       <c r="B57" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8866666666666667</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9076923076923077</v>
+        <v>0.9146341463414634</v>
       </c>
       <c r="D57" t="n">
-        <v>0.6781609195402298</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7763157894736842</v>
+        <v>0.8982035928143712</v>
       </c>
       <c r="F57" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G57" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I57" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -3133,28 +3133,28 @@
         <v>150</v>
       </c>
       <c r="B58" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8526315789473684</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.8941176470588236</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8901098901098902</v>
+        <v>0.8685714285714287</v>
       </c>
       <c r="F58" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G58" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H58" t="n">
         <v>14</v>
       </c>
       <c r="I58" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3180,28 +3180,28 @@
         <v>150</v>
       </c>
       <c r="B59" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C59" t="n">
-        <v>0.847457627118644</v>
+        <v>0.88</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5747126436781609</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="E59" t="n">
-        <v>0.684931506849315</v>
+        <v>0.825</v>
       </c>
       <c r="F59" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G59" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H59" t="n">
         <v>9</v>
       </c>
       <c r="I59" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -3227,28 +3227,28 @@
         <v>150</v>
       </c>
       <c r="B60" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9420289855072463</v>
       </c>
       <c r="D60" t="n">
-        <v>0.5747126436781609</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7092198581560283</v>
+        <v>0.8441558441558441</v>
       </c>
       <c r="F60" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G60" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H60" t="n">
         <v>4</v>
       </c>
       <c r="I60" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -3274,28 +3274,28 @@
         <v>150</v>
       </c>
       <c r="B61" t="n">
-        <v>0.76</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9180327868852459</v>
+        <v>0.9342105263157895</v>
       </c>
       <c r="D61" t="n">
-        <v>0.6436781609195402</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7567567567567568</v>
+        <v>0.8819875776397516</v>
       </c>
       <c r="F61" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H61" t="n">
         <v>5</v>
       </c>
       <c r="I61" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -3321,28 +3321,28 @@
         <v>150</v>
       </c>
       <c r="B62" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.9180327868852459</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.6588235294117647</v>
       </c>
       <c r="E62" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.7671232876712328</v>
       </c>
       <c r="F62" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G62" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H62" t="n">
         <v>5</v>
       </c>
       <c r="I62" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3368,28 +3368,28 @@
         <v>150</v>
       </c>
       <c r="B63" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.76</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9761904761904762</v>
+        <v>0.9622641509433962</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4712643678160919</v>
+        <v>0.6</v>
       </c>
       <c r="E63" t="n">
-        <v>0.6356589147286821</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="F63" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G63" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3415,28 +3415,28 @@
         <v>150</v>
       </c>
       <c r="B64" t="n">
-        <v>0.66</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.78</v>
       </c>
       <c r="D64" t="n">
-        <v>0.6551724137931034</v>
+        <v>0.9176470588235294</v>
       </c>
       <c r="E64" t="n">
-        <v>0.6909090909090909</v>
+        <v>0.8432432432432432</v>
       </c>
       <c r="F64" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="G64" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I64" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3462,28 +3462,28 @@
         <v>150</v>
       </c>
       <c r="B65" t="n">
-        <v>0.9533333333333334</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D65" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E65" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F65" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>140</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
         <v>4</v>
-      </c>
-      <c r="G65" t="n">
-        <v>139</v>
-      </c>
-      <c r="H65" t="n">
-        <v>2</v>
-      </c>
-      <c r="I65" t="n">
-        <v>5</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3509,19 +3509,19 @@
         <v>150</v>
       </c>
       <c r="B66" t="n">
-        <v>0.96</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5</v>
+        <v>0.6153846153846153</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
         <v>141</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3838,19 +3838,19 @@
         <v>150</v>
       </c>
       <c r="B73" t="n">
-        <v>0.82</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E73" t="n">
-        <v>0.2285714285714286</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
         <v>119</v>
@@ -3859,7 +3859,7 @@
         <v>22</v>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3885,28 +3885,28 @@
         <v>150</v>
       </c>
       <c r="B74" t="n">
-        <v>0.5266666666666666</v>
+        <v>0.68</v>
       </c>
       <c r="C74" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.9875</v>
       </c>
       <c r="D74" t="n">
-        <v>0.5242718446601942</v>
+        <v>0.626984126984127</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6033519553072626</v>
+        <v>0.7669902912621359</v>
       </c>
       <c r="F74" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="G74" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H74" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3932,28 +3932,28 @@
         <v>150</v>
       </c>
       <c r="B75" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.9489795918367347</v>
       </c>
       <c r="D75" t="n">
-        <v>0.6699029126213593</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7040816326530613</v>
+        <v>0.8303571428571429</v>
       </c>
       <c r="F75" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="G75" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H75" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I75" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3979,28 +3979,28 @@
         <v>150</v>
       </c>
       <c r="B76" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.76</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9629629629629629</v>
+        <v>0.96875</v>
       </c>
       <c r="D76" t="n">
-        <v>0.7572815533980582</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="E76" t="n">
-        <v>0.8478260869565217</v>
+        <v>0.8378378378378379</v>
       </c>
       <c r="F76" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="G76" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H76" t="n">
         <v>3</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -4026,28 +4026,28 @@
         <v>150</v>
       </c>
       <c r="B77" t="n">
-        <v>0.5266666666666666</v>
+        <v>0.66</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="D77" t="n">
-        <v>0.5436893203883495</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6120218579234973</v>
+        <v>0.7536231884057971</v>
       </c>
       <c r="F77" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G77" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H77" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4073,28 +4073,28 @@
         <v>150</v>
       </c>
       <c r="B78" t="n">
-        <v>0.6533333333333333</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8072289156626506</v>
+        <v>0.9880952380952381</v>
       </c>
       <c r="D78" t="n">
-        <v>0.6504854368932039</v>
+        <v>0.6587301587301587</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7204301075268817</v>
+        <v>0.7904761904761906</v>
       </c>
       <c r="F78" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G78" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H78" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -4120,28 +4120,28 @@
         <v>150</v>
       </c>
       <c r="B79" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="D79" t="n">
-        <v>0.7572815533980582</v>
+        <v>0.7936507936507936</v>
       </c>
       <c r="E79" t="n">
-        <v>0.7609756097560975</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="F79" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="G79" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H79" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4167,28 +4167,28 @@
         <v>150</v>
       </c>
       <c r="B80" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="C80" t="n">
-        <v>0.7761194029850746</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="D80" t="n">
-        <v>0.5048543689320388</v>
+        <v>0.5396825396825397</v>
       </c>
       <c r="E80" t="n">
-        <v>0.611764705882353</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="F80" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="G80" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H80" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -4214,28 +4214,28 @@
         <v>150</v>
       </c>
       <c r="B81" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.5466666666666666</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4660194174757282</v>
+        <v>0.4682539682539683</v>
       </c>
       <c r="E81" t="n">
-        <v>0.588957055214724</v>
+        <v>0.6344086021505376</v>
       </c>
       <c r="F81" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G81" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H81" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -4261,28 +4261,28 @@
         <v>150</v>
       </c>
       <c r="B82" t="n">
-        <v>0.7</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="C82" t="n">
-        <v>0.7788461538461539</v>
+        <v>0.944954128440367</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7864077669902912</v>
+        <v>0.8174603174603174</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.876595744680851</v>
       </c>
       <c r="F82" t="n">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G82" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H82" t="n">
+        <v>6</v>
+      </c>
+      <c r="I82" t="n">
         <v>23</v>
-      </c>
-      <c r="I82" t="n">
-        <v>22</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -4308,28 +4308,28 @@
         <v>150</v>
       </c>
       <c r="B83" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8113207547169812</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="D83" t="n">
-        <v>0.5584415584415584</v>
+        <v>0.7</v>
       </c>
       <c r="E83" t="n">
-        <v>0.6615384615384615</v>
+        <v>0.7887323943661972</v>
       </c>
       <c r="F83" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="G83" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H83" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I83" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -4355,28 +4355,28 @@
         <v>150</v>
       </c>
       <c r="B84" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="C84" t="n">
-        <v>0.8813559322033898</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="D84" t="n">
-        <v>0.6753246753246753</v>
+        <v>0.8</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.8533333333333333</v>
       </c>
       <c r="F84" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G84" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4405,25 +4405,25 @@
         <v>0.8533333333333334</v>
       </c>
       <c r="C85" t="n">
-        <v>0.9365079365079365</v>
+        <v>0.953125</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7662337662337663</v>
+        <v>0.7625</v>
       </c>
       <c r="E85" t="n">
-        <v>0.842857142857143</v>
+        <v>0.8472222222222222</v>
       </c>
       <c r="F85" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G85" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4449,28 +4449,28 @@
         <v>150</v>
       </c>
       <c r="B86" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.78</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.9795918367346939</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4155844155844156</v>
+        <v>0.6</v>
       </c>
       <c r="E86" t="n">
-        <v>0.5614035087719298</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="F86" t="n">
+        <v>48</v>
+      </c>
+      <c r="G86" t="n">
+        <v>69</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
         <v>32</v>
-      </c>
-      <c r="G86" t="n">
-        <v>68</v>
-      </c>
-      <c r="H86" t="n">
-        <v>5</v>
-      </c>
-      <c r="I86" t="n">
-        <v>45</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4496,28 +4496,28 @@
         <v>150</v>
       </c>
       <c r="B87" t="n">
-        <v>0.74</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C87" t="n">
-        <v>0.88</v>
+        <v>0.9661016949152542</v>
       </c>
       <c r="D87" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7125</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6929133858267715</v>
+        <v>0.8201438848920863</v>
       </c>
       <c r="F87" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G87" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4543,28 +4543,28 @@
         <v>150</v>
       </c>
       <c r="B88" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8867924528301887</v>
+        <v>0.9558823529411765</v>
       </c>
       <c r="D88" t="n">
-        <v>0.6103896103896104</v>
+        <v>0.8125</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7230769230769231</v>
+        <v>0.8783783783783784</v>
       </c>
       <c r="F88" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="G88" t="n">
         <v>67</v>
       </c>
       <c r="H88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4590,28 +4590,28 @@
         <v>150</v>
       </c>
       <c r="B89" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4805194805194805</v>
+        <v>0.6</v>
       </c>
       <c r="E89" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7328244274809161</v>
       </c>
       <c r="F89" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G89" t="n">
         <v>67</v>
       </c>
       <c r="H89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I89" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4637,28 +4637,28 @@
         <v>150</v>
       </c>
       <c r="B90" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.8723404255319149</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3766233766233766</v>
+        <v>0.5125</v>
       </c>
       <c r="E90" t="n">
-        <v>0.5</v>
+        <v>0.6456692913385826</v>
       </c>
       <c r="F90" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G90" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H90" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I90" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4684,28 +4684,28 @@
         <v>150</v>
       </c>
       <c r="B91" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8113207547169812</v>
+        <v>0.8939393939393939</v>
       </c>
       <c r="D91" t="n">
-        <v>0.5584415584415584</v>
+        <v>0.7375</v>
       </c>
       <c r="E91" t="n">
-        <v>0.6615384615384615</v>
+        <v>0.8082191780821918</v>
       </c>
       <c r="F91" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="G91" t="n">
         <v>63</v>
       </c>
       <c r="H91" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I91" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4731,28 +4731,28 @@
         <v>150</v>
       </c>
       <c r="B92" t="n">
-        <v>0.6066666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9761904761904762</v>
+        <v>0.8870967741935484</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4141414141414141</v>
+        <v>0.5913978494623656</v>
       </c>
       <c r="E92" t="n">
-        <v>0.5815602836879433</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="F92" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G92" t="n">
         <v>50</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I92" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4778,28 +4778,28 @@
         <v>150</v>
       </c>
       <c r="B93" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9375</v>
       </c>
       <c r="D93" t="n">
-        <v>0.6262626262626263</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.8670520231213872</v>
       </c>
       <c r="F93" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="G93" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I93" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4825,28 +4825,28 @@
         <v>150</v>
       </c>
       <c r="B94" t="n">
-        <v>0.8</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.8860759493670886</v>
       </c>
       <c r="D94" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7526881720430108</v>
       </c>
       <c r="E94" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8139534883720929</v>
       </c>
       <c r="F94" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G94" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H94" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I94" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4872,28 +4872,28 @@
         <v>150</v>
       </c>
       <c r="B95" t="n">
-        <v>0.66</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C95" t="n">
-        <v>0.875</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="D95" t="n">
-        <v>0.5656565656565656</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="E95" t="n">
-        <v>0.6871165644171778</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="F95" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="G95" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H95" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I95" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4919,28 +4919,28 @@
         <v>150</v>
       </c>
       <c r="B96" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="C96" t="n">
+        <v>0.9848484848484849</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.6989247311827957</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.8176100628930818</v>
+      </c>
+      <c r="F96" t="n">
+        <v>65</v>
+      </c>
+      <c r="G96" t="n">
+        <v>56</v>
+      </c>
+      <c r="H96" t="n">
         <v>1</v>
       </c>
-      <c r="D96" t="n">
-        <v>0.5252525252525253</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0.6887417218543047</v>
-      </c>
-      <c r="F96" t="n">
-        <v>52</v>
-      </c>
-      <c r="G96" t="n">
-        <v>51</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
       <c r="I96" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4966,28 +4966,28 @@
         <v>150</v>
       </c>
       <c r="B97" t="n">
-        <v>0.6466666666666666</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C97" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8875</v>
       </c>
       <c r="D97" t="n">
-        <v>0.5252525252525253</v>
+        <v>0.7634408602150538</v>
       </c>
       <c r="E97" t="n">
-        <v>0.6624203821656051</v>
+        <v>0.8208092485549132</v>
       </c>
       <c r="F97" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G97" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H97" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I97" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -5013,28 +5013,28 @@
         <v>150</v>
       </c>
       <c r="B98" t="n">
-        <v>0.6533333333333333</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8983050847457628</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="D98" t="n">
-        <v>0.5353535353535354</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="E98" t="n">
-        <v>0.6708860759493672</v>
+        <v>0.7682926829268293</v>
       </c>
       <c r="F98" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G98" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H98" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I98" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -5060,28 +5060,28 @@
         <v>150</v>
       </c>
       <c r="B99" t="n">
-        <v>0.6466666666666666</v>
+        <v>0.72</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9423076923076923</v>
+        <v>0.9322033898305084</v>
       </c>
       <c r="D99" t="n">
-        <v>0.494949494949495</v>
+        <v>0.5913978494623656</v>
       </c>
       <c r="E99" t="n">
-        <v>0.6490066225165563</v>
+        <v>0.7236842105263158</v>
       </c>
       <c r="F99" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G99" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I99" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -5107,28 +5107,28 @@
         <v>150</v>
       </c>
       <c r="B100" t="n">
-        <v>0.5266666666666666</v>
+        <v>0.6466666666666666</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.6989247311827957</v>
       </c>
       <c r="E100" t="n">
-        <v>0.5748502994011976</v>
+        <v>0.7103825136612022</v>
       </c>
       <c r="F100" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G100" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H100" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I100" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -5154,28 +5154,28 @@
         <v>150</v>
       </c>
       <c r="B101" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.88</v>
       </c>
       <c r="C101" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.9574468085106383</v>
       </c>
       <c r="D101" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7377049180327869</v>
       </c>
       <c r="E101" t="n">
-        <v>0.6363636363636365</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F101" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G101" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H101" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I101" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -5201,28 +5201,28 @@
         <v>150</v>
       </c>
       <c r="B102" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6440677966101694</v>
+        <v>0.8852459016393442</v>
       </c>
       <c r="D102" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8852459016393442</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7524752475247525</v>
+        <v>0.8852459016393442</v>
       </c>
       <c r="F102" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G102" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H102" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -5248,28 +5248,28 @@
         <v>150</v>
       </c>
       <c r="B103" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9133333333333333</v>
       </c>
       <c r="C103" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9137931034482759</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8688524590163934</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8907563025210085</v>
       </c>
       <c r="F103" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G103" t="n">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="H103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -5295,28 +5295,28 @@
         <v>150</v>
       </c>
       <c r="B104" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C104" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="D104" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6885245901639344</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.7706422018348624</v>
       </c>
       <c r="F104" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G104" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H104" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I104" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -5342,28 +5342,28 @@
         <v>150</v>
       </c>
       <c r="B105" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.84</v>
       </c>
       <c r="C105" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="D105" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6229508196721312</v>
       </c>
       <c r="E105" t="n">
-        <v>0.6419753086419754</v>
+        <v>0.76</v>
       </c>
       <c r="F105" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G105" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H105" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -5389,28 +5389,28 @@
         <v>150</v>
       </c>
       <c r="B106" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="C106" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="D106" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8524590163934426</v>
       </c>
       <c r="E106" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.8739495798319327</v>
       </c>
       <c r="F106" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G106" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H106" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -5436,28 +5436,28 @@
         <v>150</v>
       </c>
       <c r="B107" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C107" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D107" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="E107" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6990291262135924</v>
       </c>
       <c r="F107" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G107" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H107" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I107" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -5483,28 +5483,28 @@
         <v>150</v>
       </c>
       <c r="B108" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C108" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="D108" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="E108" t="n">
-        <v>0.6419753086419754</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G108" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H108" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I108" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5530,28 +5530,28 @@
         <v>150</v>
       </c>
       <c r="B109" t="n">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.691358024691358</v>
       </c>
       <c r="D109" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9180327868852459</v>
       </c>
       <c r="E109" t="n">
-        <v>0.6</v>
+        <v>0.7887323943661971</v>
       </c>
       <c r="F109" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="G109" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H109" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="I109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5577,25 +5577,25 @@
         <v>150</v>
       </c>
       <c r="B110" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.98</v>
       </c>
       <c r="C110" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="D110" t="n">
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>0.8</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F110" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G110" t="n">
         <v>126</v>
       </c>
       <c r="H110" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -5624,25 +5624,25 @@
         <v>150</v>
       </c>
       <c r="B111" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.98</v>
       </c>
       <c r="C111" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0.8</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F111" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G111" t="n">
         <v>126</v>
       </c>
       <c r="H111" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -5671,25 +5671,25 @@
         <v>150</v>
       </c>
       <c r="B112" t="n">
-        <v>0.9733333333333334</v>
+        <v>0.96</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0.888888888888889</v>
+        <v>0.8750000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G112" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H112" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -5718,25 +5718,25 @@
         <v>150</v>
       </c>
       <c r="B113" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9733333333333334</v>
       </c>
       <c r="C113" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9375</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="E113" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.9090909090909089</v>
       </c>
       <c r="F113" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G113" t="n">
         <v>126</v>
       </c>
       <c r="H113" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -5765,25 +5765,25 @@
         <v>150</v>
       </c>
       <c r="B114" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9733333333333334</v>
       </c>
       <c r="C114" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="D114" t="n">
-        <v>0.8125</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E114" t="n">
-        <v>0.742857142857143</v>
+        <v>0.9</v>
       </c>
       <c r="F114" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G114" t="n">
         <v>128</v>
       </c>
       <c r="H114" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
         <v>3</v>
@@ -5812,25 +5812,25 @@
         <v>150</v>
       </c>
       <c r="B115" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C115" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="D115" t="n">
-        <v>0.875</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="E115" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="F115" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G115" t="n">
         <v>126</v>
       </c>
       <c r="H115" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I115" t="n">
         <v>2</v>
@@ -5859,25 +5859,25 @@
         <v>150</v>
       </c>
       <c r="B116" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="D116" t="n">
-        <v>0.875</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="F116" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G116" t="n">
         <v>122</v>
       </c>
       <c r="H116" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I116" t="n">
         <v>2</v>
@@ -5906,28 +5906,28 @@
         <v>150</v>
       </c>
       <c r="B117" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C117" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D117" t="n">
-        <v>0.625</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="E117" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.742857142857143</v>
       </c>
       <c r="F117" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G117" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -5953,28 +5953,28 @@
         <v>150</v>
       </c>
       <c r="B118" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.7</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9375</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="F118" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G118" t="n">
         <v>120</v>
       </c>
       <c r="H118" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -6000,25 +6000,25 @@
         <v>150</v>
       </c>
       <c r="B119" t="n">
-        <v>0.7933333333333333</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C119" t="n">
-        <v>0.7454545454545455</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="D119" t="n">
-        <v>0.7068965517241379</v>
+        <v>0.7671232876712328</v>
       </c>
       <c r="E119" t="n">
-        <v>0.7256637168141592</v>
+        <v>0.8549618320610687</v>
       </c>
       <c r="F119" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G119" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H119" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I119" t="n">
         <v>17</v>
@@ -6047,28 +6047,28 @@
         <v>150</v>
       </c>
       <c r="B120" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="C120" t="n">
-        <v>0.726027397260274</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9137931034482759</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8091603053435115</v>
+        <v>0.9054054054054055</v>
       </c>
       <c r="F120" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="G120" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H120" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -6094,28 +6094,28 @@
         <v>150</v>
       </c>
       <c r="B121" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="C121" t="n">
-        <v>0.8771929824561403</v>
+        <v>0.9104477611940298</v>
       </c>
       <c r="D121" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8356164383561644</v>
       </c>
       <c r="E121" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.8714285714285713</v>
       </c>
       <c r="F121" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G121" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="H121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I121" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -6141,28 +6141,28 @@
         <v>150</v>
       </c>
       <c r="B122" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.78</v>
       </c>
       <c r="C122" t="n">
-        <v>0.581081081081081</v>
+        <v>0.7702702702702703</v>
       </c>
       <c r="D122" t="n">
-        <v>0.7413793103448276</v>
+        <v>0.7808219178082192</v>
       </c>
       <c r="E122" t="n">
-        <v>0.6515151515151516</v>
+        <v>0.7755102040816327</v>
       </c>
       <c r="F122" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G122" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H122" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I122" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -6188,28 +6188,28 @@
         <v>150</v>
       </c>
       <c r="B123" t="n">
-        <v>0.7933333333333333</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="C123" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.9811320754716981</v>
       </c>
       <c r="D123" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.7123287671232876</v>
       </c>
       <c r="E123" t="n">
-        <v>0.7207207207207208</v>
+        <v>0.8253968253968254</v>
       </c>
       <c r="F123" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G123" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H123" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -6235,28 +6235,28 @@
         <v>150</v>
       </c>
       <c r="B124" t="n">
-        <v>0.8</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C124" t="n">
-        <v>0.7</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="D124" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.8493150684931506</v>
       </c>
       <c r="E124" t="n">
-        <v>0.765625</v>
+        <v>0.8671328671328671</v>
       </c>
       <c r="F124" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G124" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H124" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I124" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -6282,28 +6282,28 @@
         <v>150</v>
       </c>
       <c r="B125" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="C125" t="n">
-        <v>0.6197183098591549</v>
+        <v>0.7605633802816901</v>
       </c>
       <c r="D125" t="n">
-        <v>0.7586206896551724</v>
+        <v>0.7397260273972602</v>
       </c>
       <c r="E125" t="n">
-        <v>0.6821705426356589</v>
+        <v>0.75</v>
       </c>
       <c r="F125" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G125" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H125" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I125" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -6329,28 +6329,28 @@
         <v>150</v>
       </c>
       <c r="B126" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C126" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D126" t="n">
-        <v>0.6724137931034483</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="E126" t="n">
-        <v>0.6964285714285714</v>
+        <v>0.7559055118110236</v>
       </c>
       <c r="F126" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G126" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H126" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I126" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -6376,28 +6376,28 @@
         <v>150</v>
       </c>
       <c r="B127" t="n">
-        <v>0.6066666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C127" t="n">
-        <v>0.4952380952380953</v>
+        <v>0.6513761467889908</v>
       </c>
       <c r="D127" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="E127" t="n">
-        <v>0.6380368098159509</v>
+        <v>0.7802197802197802</v>
       </c>
       <c r="F127" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G127" t="n">
         <v>39</v>
       </c>
       <c r="H127" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="I127" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -6423,19 +6423,19 @@
         <v>150</v>
       </c>
       <c r="B128" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6733333333333333</v>
       </c>
       <c r="C128" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="D128" t="n">
-        <v>0.5074626865671642</v>
+        <v>0.746268656716418</v>
       </c>
       <c r="E128" t="n">
-        <v>0.5112781954887218</v>
+        <v>0.6711409395973154</v>
       </c>
       <c r="F128" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G128" t="n">
         <v>51</v>
@@ -6444,7 +6444,7 @@
         <v>32</v>
       </c>
       <c r="I128" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -6470,28 +6470,28 @@
         <v>150</v>
       </c>
       <c r="B129" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="C129" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8142857142857143</v>
       </c>
       <c r="D129" t="n">
-        <v>0.5970149253731343</v>
+        <v>0.8507462686567164</v>
       </c>
       <c r="E129" t="n">
-        <v>0.6504065040650405</v>
+        <v>0.832116788321168</v>
       </c>
       <c r="F129" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G129" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H129" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I129" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -6517,19 +6517,19 @@
         <v>150</v>
       </c>
       <c r="B130" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="C130" t="n">
-        <v>0.734375</v>
+        <v>0.7068965517241379</v>
       </c>
       <c r="D130" t="n">
-        <v>0.7014925373134329</v>
+        <v>0.6119402985074627</v>
       </c>
       <c r="E130" t="n">
-        <v>0.7175572519083969</v>
+        <v>0.6559999999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G130" t="n">
         <v>66</v>
@@ -6538,7 +6538,7 @@
         <v>17</v>
       </c>
       <c r="I130" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6564,19 +6564,19 @@
         <v>150</v>
       </c>
       <c r="B131" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="C131" t="n">
-        <v>0.3883495145631068</v>
+        <v>0.4793388429752066</v>
       </c>
       <c r="D131" t="n">
-        <v>0.5970149253731343</v>
+        <v>0.8656716417910447</v>
       </c>
       <c r="E131" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.6170212765957447</v>
       </c>
       <c r="F131" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G131" t="n">
         <v>20</v>
@@ -6585,7 +6585,7 @@
         <v>63</v>
       </c>
       <c r="I131" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6611,19 +6611,19 @@
         <v>150</v>
       </c>
       <c r="B132" t="n">
-        <v>0.62</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="C132" t="n">
-        <v>0.65625</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="D132" t="n">
-        <v>0.3134328358208955</v>
+        <v>0.5522388059701493</v>
       </c>
       <c r="E132" t="n">
-        <v>0.4242424242424243</v>
+        <v>0.6434782608695653</v>
       </c>
       <c r="F132" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G132" t="n">
         <v>72</v>
@@ -6632,7 +6632,7 @@
         <v>11</v>
       </c>
       <c r="I132" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6658,19 +6658,19 @@
         <v>150</v>
       </c>
       <c r="B133" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="C133" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="D133" t="n">
-        <v>0.5223880597014925</v>
+        <v>0.7014925373134329</v>
       </c>
       <c r="E133" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.7401574803149608</v>
       </c>
       <c r="F133" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G133" t="n">
         <v>70</v>
@@ -6679,7 +6679,7 @@
         <v>13</v>
       </c>
       <c r="I133" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -6705,19 +6705,19 @@
         <v>150</v>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="C134" t="n">
-        <v>0.4393939393939394</v>
+        <v>0.5542168674698795</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4328358208955224</v>
+        <v>0.6865671641791045</v>
       </c>
       <c r="E134" t="n">
-        <v>0.4360902255639098</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="F134" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="G134" t="n">
         <v>46</v>
@@ -6726,7 +6726,7 @@
         <v>37</v>
       </c>
       <c r="I134" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -6752,19 +6752,19 @@
         <v>150</v>
       </c>
       <c r="B135" t="n">
-        <v>0.5933333333333334</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="C135" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="D135" t="n">
-        <v>0.2985074626865671</v>
+        <v>0.5671641791044776</v>
       </c>
       <c r="E135" t="n">
-        <v>0.396039603960396</v>
+        <v>0.6386554621848739</v>
       </c>
       <c r="F135" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G135" t="n">
         <v>69</v>
@@ -6773,7 +6773,7 @@
         <v>14</v>
       </c>
       <c r="I135" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -6799,19 +6799,19 @@
         <v>150</v>
       </c>
       <c r="B136" t="n">
-        <v>0.5266666666666666</v>
+        <v>0.6266666666666667</v>
       </c>
       <c r="C136" t="n">
-        <v>0.4743589743589743</v>
+        <v>0.5591397849462365</v>
       </c>
       <c r="D136" t="n">
-        <v>0.5522388059701493</v>
+        <v>0.7761194029850746</v>
       </c>
       <c r="E136" t="n">
-        <v>0.5103448275862068</v>
+        <v>0.65</v>
       </c>
       <c r="F136" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G136" t="n">
         <v>42</v>
@@ -6820,7 +6820,7 @@
         <v>41</v>
       </c>
       <c r="I136" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -6846,28 +6846,28 @@
         <v>150</v>
       </c>
       <c r="B137" t="n">
-        <v>0.6066666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C137" t="n">
-        <v>0.5098039215686274</v>
+        <v>0.5</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.5272727272727272</v>
       </c>
       <c r="E137" t="n">
-        <v>0.4684684684684685</v>
+        <v>0.5132743362831858</v>
       </c>
       <c r="F137" t="n">
+        <v>29</v>
+      </c>
+      <c r="G137" t="n">
+        <v>66</v>
+      </c>
+      <c r="H137" t="n">
+        <v>29</v>
+      </c>
+      <c r="I137" t="n">
         <v>26</v>
-      </c>
-      <c r="G137" t="n">
-        <v>65</v>
-      </c>
-      <c r="H137" t="n">
-        <v>25</v>
-      </c>
-      <c r="I137" t="n">
-        <v>34</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -6893,28 +6893,28 @@
         <v>150</v>
       </c>
       <c r="B138" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C138" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.711864406779661</v>
       </c>
       <c r="D138" t="n">
-        <v>0.6</v>
+        <v>0.7636363636363637</v>
       </c>
       <c r="E138" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.736842105263158</v>
       </c>
       <c r="F138" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G138" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H138" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I138" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -6940,28 +6940,28 @@
         <v>150</v>
       </c>
       <c r="B139" t="n">
-        <v>0.66</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C139" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3090909090909091</v>
       </c>
       <c r="E139" t="n">
-        <v>0.4950495049504951</v>
+        <v>0.3820224719101123</v>
       </c>
       <c r="F139" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G139" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H139" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I139" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -6987,28 +6987,28 @@
         <v>150</v>
       </c>
       <c r="B140" t="n">
-        <v>0.34</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="D140" t="n">
-        <v>0.45</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3529411764705882</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="F140" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G140" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H140" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I140" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -7034,28 +7034,28 @@
         <v>150</v>
       </c>
       <c r="B141" t="n">
-        <v>0.62</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="C141" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2</v>
+        <v>0.3818181818181818</v>
       </c>
       <c r="E141" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.4772727272727273</v>
       </c>
       <c r="F141" t="n">
+        <v>21</v>
+      </c>
+      <c r="G141" t="n">
+        <v>83</v>
+      </c>
+      <c r="H141" t="n">
         <v>12</v>
       </c>
-      <c r="G141" t="n">
-        <v>81</v>
-      </c>
-      <c r="H141" t="n">
-        <v>9</v>
-      </c>
       <c r="I141" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -7081,28 +7081,28 @@
         <v>150</v>
       </c>
       <c r="B142" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.72</v>
       </c>
       <c r="C142" t="n">
-        <v>0.65625</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="D142" t="n">
-        <v>0.35</v>
+        <v>0.4909090909090909</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4565217391304347</v>
+        <v>0.5625</v>
       </c>
       <c r="F142" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G142" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H142" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I142" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -7128,28 +7128,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.5466666666666666</v>
       </c>
       <c r="C143" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3166666666666667</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="E143" t="n">
-        <v>0.3247863247863248</v>
+        <v>0.46875</v>
       </c>
       <c r="F143" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G143" t="n">
         <v>52</v>
       </c>
       <c r="H143" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I143" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -7175,28 +7175,28 @@
         <v>150</v>
       </c>
       <c r="B144" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C144" t="n">
-        <v>0.4375</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="D144" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.4318181818181818</v>
       </c>
       <c r="F144" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G144" t="n">
         <v>81</v>
       </c>
       <c r="H144" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I144" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -7222,28 +7222,28 @@
         <v>150</v>
       </c>
       <c r="B145" t="n">
-        <v>0.52</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C145" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="D145" t="n">
-        <v>0.35</v>
+        <v>0.4727272727272727</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F145" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G145" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H145" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I145" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -7350,25 +7350,25 @@
         <v>150</v>
       </c>
       <c r="B2" t="n">
-        <v>0.86</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9263157894736842</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D2" t="n">
         <v>0.8627450980392157</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8934010152284264</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F2" t="n">
         <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>14</v>
@@ -7397,19 +7397,19 @@
         <v>150</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.92</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9215686274509803</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9306930693069307</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="F3" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G3" t="n">
         <v>42</v>
@@ -7418,7 +7418,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -7726,19 +7726,19 @@
         <v>150</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7424242424242424</v>
+        <v>0.75</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9607843137254902</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8376068376068376</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F10" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G10" t="n">
         <v>14</v>
@@ -7747,7 +7747,7 @@
         <v>34</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -8149,19 +8149,19 @@
         <v>150</v>
       </c>
       <c r="B19" t="n">
-        <v>0.7466666666666667</v>
+        <v>0.7533333333333333</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.421875</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9629629629629629</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.5934065934065934</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>86</v>
@@ -8170,7 +8170,7 @@
         <v>37</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -8196,28 +8196,28 @@
         <v>150</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9733333333333334</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8163265306122449</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="F20" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G20" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -8243,25 +8243,25 @@
         <v>150</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7307692307692307</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8085106382978723</v>
+        <v>0.962962962962963</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G21" t="n">
         <v>122</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>2</v>
@@ -8293,19 +8293,19 @@
         <v>0.9533333333333334</v>
       </c>
       <c r="C22" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G22" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H22" t="n">
         <v>7</v>
@@ -8337,25 +8337,25 @@
         <v>150</v>
       </c>
       <c r="B23" t="n">
-        <v>0.8733333333333333</v>
+        <v>0.92</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6779661016949152</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
         <v>111</v>
       </c>
       <c r="H23" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -8384,28 +8384,28 @@
         <v>150</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9466666666666667</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="E24" t="n">
-        <v>0.888888888888889</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="F24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -8431,25 +8431,25 @@
         <v>150</v>
       </c>
       <c r="B25" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.8852459016393442</v>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G25" t="n">
         <v>116</v>
       </c>
       <c r="H25" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -8478,25 +8478,25 @@
         <v>150</v>
       </c>
       <c r="B26" t="n">
-        <v>0.8266666666666667</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.7164179104477612</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
         <v>107</v>
       </c>
       <c r="H26" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="I26" t="n">
         <v>4</v>
@@ -8525,28 +8525,28 @@
         <v>150</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.86</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.6440677966101694</v>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H27" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -8572,28 +8572,28 @@
         <v>150</v>
       </c>
       <c r="B28" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.5869565217391305</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9642857142857143</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5757575757575758</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G28" t="n">
         <v>103</v>
       </c>
       <c r="H28" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -8619,28 +8619,28 @@
         <v>150</v>
       </c>
       <c r="B29" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.7</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -8666,19 +8666,19 @@
         <v>150</v>
       </c>
       <c r="B30" t="n">
-        <v>0.9266666666666666</v>
+        <v>0.96</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G30" t="n">
         <v>124</v>
@@ -8687,7 +8687,7 @@
         <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -8713,19 +8713,19 @@
         <v>150</v>
       </c>
       <c r="B31" t="n">
-        <v>0.9933333333333333</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9777777777777777</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="F31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G31" t="n">
         <v>127</v>
@@ -8734,7 +8734,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -8760,19 +8760,19 @@
         <v>150</v>
       </c>
       <c r="B32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.9268292682926829</v>
       </c>
       <c r="F32" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G32" t="n">
         <v>128</v>
@@ -8781,7 +8781,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -8807,19 +8807,19 @@
         <v>150</v>
       </c>
       <c r="B33" t="n">
-        <v>0.9533333333333334</v>
+        <v>0.98</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.9268292682926829</v>
       </c>
       <c r="F33" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G33" t="n">
         <v>128</v>
@@ -8828,7 +8828,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -8854,19 +8854,19 @@
         <v>150</v>
       </c>
       <c r="B34" t="n">
-        <v>0.9533333333333334</v>
+        <v>0.9933333333333333</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.9767441860465117</v>
       </c>
       <c r="F34" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G34" t="n">
         <v>128</v>
@@ -8875,7 +8875,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -8901,19 +8901,19 @@
         <v>150</v>
       </c>
       <c r="B35" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.9268292682926829</v>
       </c>
       <c r="F35" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G35" t="n">
         <v>128</v>
@@ -8922,7 +8922,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -8948,19 +8948,19 @@
         <v>150</v>
       </c>
       <c r="B36" t="n">
-        <v>0.9266666666666666</v>
+        <v>0.9533333333333334</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="E36" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G36" t="n">
         <v>128</v>
@@ -8969,7 +8969,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -8995,19 +8995,19 @@
         <v>150</v>
       </c>
       <c r="B37" t="n">
-        <v>0.92</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.84</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.8936170212765958</v>
       </c>
       <c r="F37" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G37" t="n">
         <v>124</v>
@@ -9016,7 +9016,7 @@
         <v>4</v>
       </c>
       <c r="I37" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -9042,28 +9042,28 @@
         <v>150</v>
       </c>
       <c r="B38" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8714285714285714</v>
+        <v>0.9375</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6354166666666666</v>
+        <v>0.7425742574257426</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7349397590361446</v>
+        <v>0.8287292817679558</v>
       </c>
       <c r="F38" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="G38" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I38" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -9089,28 +9089,28 @@
         <v>150</v>
       </c>
       <c r="B39" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8767123287671232</v>
+        <v>0.95</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7524752475247525</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7573964497041421</v>
+        <v>0.8397790055248618</v>
       </c>
       <c r="F39" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G39" t="n">
         <v>45</v>
       </c>
       <c r="H39" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -9136,28 +9136,28 @@
         <v>150</v>
       </c>
       <c r="B40" t="n">
-        <v>0.86</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9518072289156626</v>
+        <v>0.9294117647058824</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.7821782178217822</v>
       </c>
       <c r="E40" t="n">
-        <v>0.88268156424581</v>
+        <v>0.8494623655913979</v>
       </c>
       <c r="F40" t="n">
         <v>79</v>
       </c>
       <c r="G40" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -9183,28 +9183,28 @@
         <v>150</v>
       </c>
       <c r="B41" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.8</v>
       </c>
       <c r="C41" t="n">
-        <v>0.855072463768116</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6145833333333334</v>
+        <v>0.7425742574257426</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7151515151515152</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F41" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G41" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I41" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -9230,28 +9230,28 @@
         <v>150</v>
       </c>
       <c r="B42" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.78</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8983050847457628</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.6732673267326733</v>
       </c>
       <c r="E42" t="n">
-        <v>0.6838709677419356</v>
+        <v>0.8047337278106509</v>
       </c>
       <c r="F42" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="G42" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -9277,28 +9277,28 @@
         <v>150</v>
       </c>
       <c r="B43" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8767123287671232</v>
+        <v>0.9634146341463414</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7821782178217822</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7573964497041421</v>
+        <v>0.8633879781420765</v>
       </c>
       <c r="F43" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="G43" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H43" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -9324,28 +9324,28 @@
         <v>150</v>
       </c>
       <c r="B44" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8688524590163934</v>
+        <v>0.9402985074626866</v>
       </c>
       <c r="D44" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.6237623762376238</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6751592356687898</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G44" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -9371,28 +9371,28 @@
         <v>150</v>
       </c>
       <c r="B45" t="n">
-        <v>0.68</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9137931034482759</v>
+        <v>0.953125</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.6039603960396039</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6883116883116883</v>
+        <v>0.7393939393939394</v>
       </c>
       <c r="F45" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G45" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -9418,28 +9418,28 @@
         <v>150</v>
       </c>
       <c r="B46" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7948717948717948</v>
+        <v>0.851063829787234</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.7920792079207921</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7126436781609194</v>
+        <v>0.8205128205128204</v>
       </c>
       <c r="F46" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G46" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H46" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I46" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -9465,28 +9465,28 @@
         <v>150</v>
       </c>
       <c r="B47" t="n">
-        <v>0.6266666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9148936170212766</v>
+        <v>0.9242424242424242</v>
       </c>
       <c r="D47" t="n">
-        <v>0.4526315789473684</v>
+        <v>0.6630434782608695</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6056338028169014</v>
+        <v>0.7721518987341771</v>
       </c>
       <c r="F47" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="G47" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -9512,28 +9512,28 @@
         <v>150</v>
       </c>
       <c r="B48" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.88</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9264705882352942</v>
+        <v>0.9204545454545454</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6631578947368421</v>
+        <v>0.8804347826086957</v>
       </c>
       <c r="E48" t="n">
-        <v>0.773006134969325</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="G48" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I48" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -9559,28 +9559,28 @@
         <v>150</v>
       </c>
       <c r="B49" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8210526315789474</v>
+        <v>0.83</v>
       </c>
       <c r="D49" t="n">
-        <v>0.8210526315789474</v>
+        <v>0.9021739130434783</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8210526315789475</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="F49" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G49" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H49" t="n">
         <v>17</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -9606,28 +9606,28 @@
         <v>150</v>
       </c>
       <c r="B50" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="D50" t="n">
-        <v>0.5368421052631579</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6496815286624203</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G50" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H50" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I50" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -9653,28 +9653,28 @@
         <v>150</v>
       </c>
       <c r="B51" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.84</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9482758620689655</v>
+        <v>0.9594594594594594</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.7717391304347826</v>
       </c>
       <c r="E51" t="n">
-        <v>0.7189542483660131</v>
+        <v>0.855421686746988</v>
       </c>
       <c r="F51" t="n">
+        <v>71</v>
+      </c>
+      <c r="G51" t="n">
         <v>55</v>
-      </c>
-      <c r="G51" t="n">
-        <v>52</v>
       </c>
       <c r="H51" t="n">
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -9700,28 +9700,28 @@
         <v>150</v>
       </c>
       <c r="B52" t="n">
-        <v>0.74</v>
+        <v>0.8866666666666667</v>
       </c>
       <c r="C52" t="n">
-        <v>0.9516129032258065</v>
+        <v>0.9746835443037974</v>
       </c>
       <c r="D52" t="n">
-        <v>0.6210526315789474</v>
+        <v>0.8369565217391305</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7515923566878981</v>
+        <v>0.9005847953216375</v>
       </c>
       <c r="F52" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="G52" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -9747,28 +9747,28 @@
         <v>150</v>
       </c>
       <c r="B53" t="n">
-        <v>0.5933333333333334</v>
+        <v>0.68</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9722222222222222</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5343511450381679</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="F53" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G53" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -9794,28 +9794,28 @@
         <v>150</v>
       </c>
       <c r="B54" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8936170212765957</v>
+        <v>0.9322033898305084</v>
       </c>
       <c r="D54" t="n">
-        <v>0.4421052631578947</v>
+        <v>0.5978260869565217</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5915492957746478</v>
+        <v>0.728476821192053</v>
       </c>
       <c r="F54" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G54" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I54" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -9841,28 +9841,28 @@
         <v>150</v>
       </c>
       <c r="B55" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.8470588235294118</v>
       </c>
       <c r="D55" t="n">
-        <v>0.5473684210526316</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="E55" t="n">
-        <v>0.6459627329192547</v>
+        <v>0.8135593220338984</v>
       </c>
       <c r="F55" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G55" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H55" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I55" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -9888,28 +9888,28 @@
         <v>150</v>
       </c>
       <c r="B56" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8909090909090909</v>
+        <v>0.9041095890410958</v>
       </c>
       <c r="D56" t="n">
-        <v>0.5632183908045977</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6901408450704224</v>
+        <v>0.8354430379746836</v>
       </c>
       <c r="F56" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G56" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I56" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -9935,28 +9935,28 @@
         <v>150</v>
       </c>
       <c r="B57" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8866666666666667</v>
       </c>
       <c r="C57" t="n">
-        <v>0.9076923076923077</v>
+        <v>0.9146341463414634</v>
       </c>
       <c r="D57" t="n">
-        <v>0.6781609195402298</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7763157894736842</v>
+        <v>0.8982035928143712</v>
       </c>
       <c r="F57" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="G57" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I57" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -9982,28 +9982,28 @@
         <v>150</v>
       </c>
       <c r="B58" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8526315789473684</v>
+        <v>0.8444444444444444</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.8941176470588236</v>
       </c>
       <c r="E58" t="n">
-        <v>0.8901098901098902</v>
+        <v>0.8685714285714287</v>
       </c>
       <c r="F58" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G58" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H58" t="n">
         <v>14</v>
       </c>
       <c r="I58" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -10029,28 +10029,28 @@
         <v>150</v>
       </c>
       <c r="B59" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C59" t="n">
-        <v>0.847457627118644</v>
+        <v>0.88</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5747126436781609</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="E59" t="n">
-        <v>0.684931506849315</v>
+        <v>0.825</v>
       </c>
       <c r="F59" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G59" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H59" t="n">
         <v>9</v>
       </c>
       <c r="I59" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -10076,28 +10076,28 @@
         <v>150</v>
       </c>
       <c r="B60" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9420289855072463</v>
       </c>
       <c r="D60" t="n">
-        <v>0.5747126436781609</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="E60" t="n">
-        <v>0.7092198581560283</v>
+        <v>0.8441558441558441</v>
       </c>
       <c r="F60" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="G60" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H60" t="n">
         <v>4</v>
       </c>
       <c r="I60" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -10123,28 +10123,28 @@
         <v>150</v>
       </c>
       <c r="B61" t="n">
-        <v>0.76</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C61" t="n">
-        <v>0.9180327868852459</v>
+        <v>0.9342105263157895</v>
       </c>
       <c r="D61" t="n">
-        <v>0.6436781609195402</v>
+        <v>0.8352941176470589</v>
       </c>
       <c r="E61" t="n">
-        <v>0.7567567567567568</v>
+        <v>0.8819875776397516</v>
       </c>
       <c r="F61" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H61" t="n">
         <v>5</v>
       </c>
       <c r="I61" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -10170,28 +10170,28 @@
         <v>150</v>
       </c>
       <c r="B62" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.9180327868852459</v>
       </c>
       <c r="D62" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.6588235294117647</v>
       </c>
       <c r="E62" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.7671232876712328</v>
       </c>
       <c r="F62" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G62" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H62" t="n">
         <v>5</v>
       </c>
       <c r="I62" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -10217,28 +10217,28 @@
         <v>150</v>
       </c>
       <c r="B63" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.76</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9761904761904762</v>
+        <v>0.9622641509433962</v>
       </c>
       <c r="D63" t="n">
-        <v>0.4712643678160919</v>
+        <v>0.6</v>
       </c>
       <c r="E63" t="n">
-        <v>0.6356589147286821</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="F63" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G63" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -10264,28 +10264,28 @@
         <v>150</v>
       </c>
       <c r="B64" t="n">
-        <v>0.66</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="C64" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.78</v>
       </c>
       <c r="D64" t="n">
-        <v>0.6551724137931034</v>
+        <v>0.9176470588235294</v>
       </c>
       <c r="E64" t="n">
-        <v>0.6909090909090909</v>
+        <v>0.8432432432432432</v>
       </c>
       <c r="F64" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="G64" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H64" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I64" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -10311,28 +10311,28 @@
         <v>150</v>
       </c>
       <c r="B65" t="n">
-        <v>0.9533333333333334</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D65" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E65" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="F65" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>140</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" t="n">
         <v>4</v>
-      </c>
-      <c r="G65" t="n">
-        <v>139</v>
-      </c>
-      <c r="H65" t="n">
-        <v>2</v>
-      </c>
-      <c r="I65" t="n">
-        <v>5</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -10358,19 +10358,19 @@
         <v>150</v>
       </c>
       <c r="B66" t="n">
-        <v>0.96</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5</v>
+        <v>0.6153846153846153</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="n">
         <v>141</v>
@@ -10379,7 +10379,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -10687,19 +10687,19 @@
         <v>150</v>
       </c>
       <c r="B73" t="n">
-        <v>0.82</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E73" t="n">
-        <v>0.2285714285714286</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G73" t="n">
         <v>119</v>
@@ -10708,7 +10708,7 @@
         <v>22</v>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -10734,28 +10734,28 @@
         <v>150</v>
       </c>
       <c r="B74" t="n">
-        <v>0.5266666666666666</v>
+        <v>0.68</v>
       </c>
       <c r="C74" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.9875</v>
       </c>
       <c r="D74" t="n">
-        <v>0.5242718446601942</v>
+        <v>0.626984126984127</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6033519553072626</v>
+        <v>0.7669902912621359</v>
       </c>
       <c r="F74" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="G74" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H74" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -10781,28 +10781,28 @@
         <v>150</v>
       </c>
       <c r="B75" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.9489795918367347</v>
       </c>
       <c r="D75" t="n">
-        <v>0.6699029126213593</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="E75" t="n">
-        <v>0.7040816326530613</v>
+        <v>0.8303571428571429</v>
       </c>
       <c r="F75" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="G75" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H75" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I75" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -10828,28 +10828,28 @@
         <v>150</v>
       </c>
       <c r="B76" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.76</v>
       </c>
       <c r="C76" t="n">
-        <v>0.9629629629629629</v>
+        <v>0.96875</v>
       </c>
       <c r="D76" t="n">
-        <v>0.7572815533980582</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="E76" t="n">
-        <v>0.8478260869565217</v>
+        <v>0.8378378378378379</v>
       </c>
       <c r="F76" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="G76" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H76" t="n">
         <v>3</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -10875,28 +10875,28 @@
         <v>150</v>
       </c>
       <c r="B77" t="n">
-        <v>0.5266666666666666</v>
+        <v>0.66</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7</v>
+        <v>0.9629629629629629</v>
       </c>
       <c r="D77" t="n">
-        <v>0.5436893203883495</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6120218579234973</v>
+        <v>0.7536231884057971</v>
       </c>
       <c r="F77" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="G77" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H77" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -10922,28 +10922,28 @@
         <v>150</v>
       </c>
       <c r="B78" t="n">
-        <v>0.6533333333333333</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8072289156626506</v>
+        <v>0.9880952380952381</v>
       </c>
       <c r="D78" t="n">
-        <v>0.6504854368932039</v>
+        <v>0.6587301587301587</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7204301075268817</v>
+        <v>0.7904761904761906</v>
       </c>
       <c r="F78" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G78" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H78" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -10969,28 +10969,28 @@
         <v>150</v>
       </c>
       <c r="B79" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="D79" t="n">
-        <v>0.7572815533980582</v>
+        <v>0.7936507936507936</v>
       </c>
       <c r="E79" t="n">
-        <v>0.7609756097560975</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="F79" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="G79" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H79" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -11016,28 +11016,28 @@
         <v>150</v>
       </c>
       <c r="B80" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="C80" t="n">
-        <v>0.7761194029850746</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="D80" t="n">
-        <v>0.5048543689320388</v>
+        <v>0.5396825396825397</v>
       </c>
       <c r="E80" t="n">
-        <v>0.611764705882353</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="F80" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="G80" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H80" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -11063,28 +11063,28 @@
         <v>150</v>
       </c>
       <c r="B81" t="n">
-        <v>0.5533333333333333</v>
+        <v>0.5466666666666666</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8</v>
+        <v>0.9833333333333333</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4660194174757282</v>
+        <v>0.4682539682539683</v>
       </c>
       <c r="E81" t="n">
-        <v>0.588957055214724</v>
+        <v>0.6344086021505376</v>
       </c>
       <c r="F81" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G81" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H81" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -11110,28 +11110,28 @@
         <v>150</v>
       </c>
       <c r="B82" t="n">
-        <v>0.7</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="C82" t="n">
-        <v>0.7788461538461539</v>
+        <v>0.944954128440367</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7864077669902912</v>
+        <v>0.8174603174603174</v>
       </c>
       <c r="E82" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.876595744680851</v>
       </c>
       <c r="F82" t="n">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="G82" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H82" t="n">
+        <v>6</v>
+      </c>
+      <c r="I82" t="n">
         <v>23</v>
-      </c>
-      <c r="I82" t="n">
-        <v>22</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -11157,28 +11157,28 @@
         <v>150</v>
       </c>
       <c r="B83" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8113207547169812</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="D83" t="n">
-        <v>0.5584415584415584</v>
+        <v>0.7</v>
       </c>
       <c r="E83" t="n">
-        <v>0.6615384615384615</v>
+        <v>0.7887323943661972</v>
       </c>
       <c r="F83" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="G83" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H83" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I83" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -11204,28 +11204,28 @@
         <v>150</v>
       </c>
       <c r="B84" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="C84" t="n">
-        <v>0.8813559322033898</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="D84" t="n">
-        <v>0.6753246753246753</v>
+        <v>0.8</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.8533333333333333</v>
       </c>
       <c r="F84" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="G84" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -11254,25 +11254,25 @@
         <v>0.8533333333333334</v>
       </c>
       <c r="C85" t="n">
-        <v>0.9365079365079365</v>
+        <v>0.953125</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7662337662337663</v>
+        <v>0.7625</v>
       </c>
       <c r="E85" t="n">
-        <v>0.842857142857143</v>
+        <v>0.8472222222222222</v>
       </c>
       <c r="F85" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G85" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -11298,28 +11298,28 @@
         <v>150</v>
       </c>
       <c r="B86" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.78</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.9795918367346939</v>
       </c>
       <c r="D86" t="n">
-        <v>0.4155844155844156</v>
+        <v>0.6</v>
       </c>
       <c r="E86" t="n">
-        <v>0.5614035087719298</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="F86" t="n">
+        <v>48</v>
+      </c>
+      <c r="G86" t="n">
+        <v>69</v>
+      </c>
+      <c r="H86" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" t="n">
         <v>32</v>
-      </c>
-      <c r="G86" t="n">
-        <v>68</v>
-      </c>
-      <c r="H86" t="n">
-        <v>5</v>
-      </c>
-      <c r="I86" t="n">
-        <v>45</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -11345,28 +11345,28 @@
         <v>150</v>
       </c>
       <c r="B87" t="n">
-        <v>0.74</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C87" t="n">
-        <v>0.88</v>
+        <v>0.9661016949152542</v>
       </c>
       <c r="D87" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7125</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6929133858267715</v>
+        <v>0.8201438848920863</v>
       </c>
       <c r="F87" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G87" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I87" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -11392,28 +11392,28 @@
         <v>150</v>
       </c>
       <c r="B88" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8867924528301887</v>
+        <v>0.9558823529411765</v>
       </c>
       <c r="D88" t="n">
-        <v>0.6103896103896104</v>
+        <v>0.8125</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7230769230769231</v>
+        <v>0.8783783783783784</v>
       </c>
       <c r="F88" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="G88" t="n">
         <v>67</v>
       </c>
       <c r="H88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -11439,28 +11439,28 @@
         <v>150</v>
       </c>
       <c r="B89" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="D89" t="n">
-        <v>0.4805194805194805</v>
+        <v>0.6</v>
       </c>
       <c r="E89" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.7328244274809161</v>
       </c>
       <c r="F89" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G89" t="n">
         <v>67</v>
       </c>
       <c r="H89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I89" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -11486,28 +11486,28 @@
         <v>150</v>
       </c>
       <c r="B90" t="n">
-        <v>0.6133333333333333</v>
+        <v>0.7</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.8723404255319149</v>
       </c>
       <c r="D90" t="n">
-        <v>0.3766233766233766</v>
+        <v>0.5125</v>
       </c>
       <c r="E90" t="n">
-        <v>0.5</v>
+        <v>0.6456692913385826</v>
       </c>
       <c r="F90" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G90" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H90" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I90" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -11533,28 +11533,28 @@
         <v>150</v>
       </c>
       <c r="B91" t="n">
-        <v>0.7066666666666667</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8113207547169812</v>
+        <v>0.8939393939393939</v>
       </c>
       <c r="D91" t="n">
-        <v>0.5584415584415584</v>
+        <v>0.7375</v>
       </c>
       <c r="E91" t="n">
-        <v>0.6615384615384615</v>
+        <v>0.8082191780821918</v>
       </c>
       <c r="F91" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="G91" t="n">
         <v>63</v>
       </c>
       <c r="H91" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I91" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -11580,28 +11580,28 @@
         <v>150</v>
       </c>
       <c r="B92" t="n">
-        <v>0.6066666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="C92" t="n">
-        <v>0.9761904761904762</v>
+        <v>0.8870967741935484</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4141414141414141</v>
+        <v>0.5913978494623656</v>
       </c>
       <c r="E92" t="n">
-        <v>0.5815602836879433</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="F92" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G92" t="n">
         <v>50</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I92" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -11627,28 +11627,28 @@
         <v>150</v>
       </c>
       <c r="B93" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="C93" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9375</v>
       </c>
       <c r="D93" t="n">
-        <v>0.6262626262626263</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.8670520231213872</v>
       </c>
       <c r="F93" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="G93" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I93" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -11674,28 +11674,28 @@
         <v>150</v>
       </c>
       <c r="B94" t="n">
-        <v>0.8</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.8860759493670886</v>
       </c>
       <c r="D94" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7526881720430108</v>
       </c>
       <c r="E94" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8139534883720929</v>
       </c>
       <c r="F94" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G94" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H94" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I94" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -11721,28 +11721,28 @@
         <v>150</v>
       </c>
       <c r="B95" t="n">
-        <v>0.66</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C95" t="n">
-        <v>0.875</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="D95" t="n">
-        <v>0.5656565656565656</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="E95" t="n">
-        <v>0.6871165644171778</v>
+        <v>0.8228571428571428</v>
       </c>
       <c r="F95" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="G95" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H95" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I95" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -11768,28 +11768,28 @@
         <v>150</v>
       </c>
       <c r="B96" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="C96" t="n">
+        <v>0.9848484848484849</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.6989247311827957</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.8176100628930818</v>
+      </c>
+      <c r="F96" t="n">
+        <v>65</v>
+      </c>
+      <c r="G96" t="n">
+        <v>56</v>
+      </c>
+      <c r="H96" t="n">
         <v>1</v>
       </c>
-      <c r="D96" t="n">
-        <v>0.5252525252525253</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0.6887417218543047</v>
-      </c>
-      <c r="F96" t="n">
-        <v>52</v>
-      </c>
-      <c r="G96" t="n">
-        <v>51</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
       <c r="I96" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -11815,28 +11815,28 @@
         <v>150</v>
       </c>
       <c r="B97" t="n">
-        <v>0.6466666666666666</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C97" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8875</v>
       </c>
       <c r="D97" t="n">
-        <v>0.5252525252525253</v>
+        <v>0.7634408602150538</v>
       </c>
       <c r="E97" t="n">
-        <v>0.6624203821656051</v>
+        <v>0.8208092485549132</v>
       </c>
       <c r="F97" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G97" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H97" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I97" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -11862,28 +11862,28 @@
         <v>150</v>
       </c>
       <c r="B98" t="n">
-        <v>0.6533333333333333</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="C98" t="n">
-        <v>0.8983050847457628</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="D98" t="n">
-        <v>0.5353535353535354</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="E98" t="n">
-        <v>0.6708860759493672</v>
+        <v>0.7682926829268293</v>
       </c>
       <c r="F98" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="G98" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H98" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I98" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -11909,28 +11909,28 @@
         <v>150</v>
       </c>
       <c r="B99" t="n">
-        <v>0.6466666666666666</v>
+        <v>0.72</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9423076923076923</v>
+        <v>0.9322033898305084</v>
       </c>
       <c r="D99" t="n">
-        <v>0.494949494949495</v>
+        <v>0.5913978494623656</v>
       </c>
       <c r="E99" t="n">
-        <v>0.6490066225165563</v>
+        <v>0.7236842105263158</v>
       </c>
       <c r="F99" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G99" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="H99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I99" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -11956,28 +11956,28 @@
         <v>150</v>
       </c>
       <c r="B100" t="n">
-        <v>0.5266666666666666</v>
+        <v>0.6466666666666666</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.6989247311827957</v>
       </c>
       <c r="E100" t="n">
-        <v>0.5748502994011976</v>
+        <v>0.7103825136612022</v>
       </c>
       <c r="F100" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G100" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H100" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I100" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -12003,28 +12003,28 @@
         <v>150</v>
       </c>
       <c r="B101" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.88</v>
       </c>
       <c r="C101" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.9574468085106383</v>
       </c>
       <c r="D101" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7377049180327869</v>
       </c>
       <c r="E101" t="n">
-        <v>0.6363636363636365</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F101" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="G101" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H101" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I101" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -12050,28 +12050,28 @@
         <v>150</v>
       </c>
       <c r="B102" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="C102" t="n">
-        <v>0.6440677966101694</v>
+        <v>0.8852459016393442</v>
       </c>
       <c r="D102" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8852459016393442</v>
       </c>
       <c r="E102" t="n">
-        <v>0.7524752475247525</v>
+        <v>0.8852459016393442</v>
       </c>
       <c r="F102" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G102" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H102" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I102" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -12097,28 +12097,28 @@
         <v>150</v>
       </c>
       <c r="B103" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9133333333333333</v>
       </c>
       <c r="C103" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9137931034482759</v>
       </c>
       <c r="D103" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8688524590163934</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8907563025210085</v>
       </c>
       <c r="F103" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G103" t="n">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="H103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -12144,28 +12144,28 @@
         <v>150</v>
       </c>
       <c r="B104" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="C104" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="D104" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6885245901639344</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.7706422018348624</v>
       </c>
       <c r="F104" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G104" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H104" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I104" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -12191,28 +12191,28 @@
         <v>150</v>
       </c>
       <c r="B105" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.84</v>
       </c>
       <c r="C105" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9743589743589743</v>
       </c>
       <c r="D105" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6229508196721312</v>
       </c>
       <c r="E105" t="n">
-        <v>0.6419753086419754</v>
+        <v>0.76</v>
       </c>
       <c r="F105" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G105" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H105" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -12238,28 +12238,28 @@
         <v>150</v>
       </c>
       <c r="B106" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.9</v>
       </c>
       <c r="C106" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="D106" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8524590163934426</v>
       </c>
       <c r="E106" t="n">
-        <v>0.7200000000000001</v>
+        <v>0.8739495798319327</v>
       </c>
       <c r="F106" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G106" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H106" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -12285,28 +12285,28 @@
         <v>150</v>
       </c>
       <c r="B107" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C107" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D107" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="E107" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6990291262135924</v>
       </c>
       <c r="F107" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G107" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="H107" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I107" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -12332,28 +12332,28 @@
         <v>150</v>
       </c>
       <c r="B108" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="C108" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="D108" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="E108" t="n">
-        <v>0.6419753086419754</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G108" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H108" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I108" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -12379,28 +12379,28 @@
         <v>150</v>
       </c>
       <c r="B109" t="n">
-        <v>0.68</v>
+        <v>0.8</v>
       </c>
       <c r="C109" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.691358024691358</v>
       </c>
       <c r="D109" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9180327868852459</v>
       </c>
       <c r="E109" t="n">
-        <v>0.6</v>
+        <v>0.7887323943661971</v>
       </c>
       <c r="F109" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="G109" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H109" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="I109" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -12426,25 +12426,25 @@
         <v>150</v>
       </c>
       <c r="B110" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.98</v>
       </c>
       <c r="C110" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="D110" t="n">
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>0.8</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F110" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G110" t="n">
         <v>126</v>
       </c>
       <c r="H110" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -12473,25 +12473,25 @@
         <v>150</v>
       </c>
       <c r="B111" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.98</v>
       </c>
       <c r="C111" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.875</v>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0.8</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="F111" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G111" t="n">
         <v>126</v>
       </c>
       <c r="H111" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -12520,25 +12520,25 @@
         <v>150</v>
       </c>
       <c r="B112" t="n">
-        <v>0.9733333333333334</v>
+        <v>0.96</v>
       </c>
       <c r="C112" t="n">
-        <v>0.8</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0.888888888888889</v>
+        <v>0.8750000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G112" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H112" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -12567,25 +12567,25 @@
         <v>150</v>
       </c>
       <c r="B113" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9733333333333334</v>
       </c>
       <c r="C113" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="D113" t="n">
-        <v>0.9375</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="E113" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.9090909090909089</v>
       </c>
       <c r="F113" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G113" t="n">
         <v>126</v>
       </c>
       <c r="H113" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I113" t="n">
         <v>1</v>
@@ -12614,25 +12614,25 @@
         <v>150</v>
       </c>
       <c r="B114" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9733333333333334</v>
       </c>
       <c r="C114" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="D114" t="n">
-        <v>0.8125</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E114" t="n">
-        <v>0.742857142857143</v>
+        <v>0.9</v>
       </c>
       <c r="F114" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G114" t="n">
         <v>128</v>
       </c>
       <c r="H114" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
         <v>3</v>
@@ -12661,25 +12661,25 @@
         <v>150</v>
       </c>
       <c r="B115" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="C115" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="D115" t="n">
-        <v>0.875</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="E115" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.8837209302325582</v>
       </c>
       <c r="F115" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G115" t="n">
         <v>126</v>
       </c>
       <c r="H115" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I115" t="n">
         <v>2</v>
@@ -12708,25 +12708,25 @@
         <v>150</v>
       </c>
       <c r="B116" t="n">
-        <v>0.9066666666666666</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="D116" t="n">
-        <v>0.875</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="F116" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G116" t="n">
         <v>122</v>
       </c>
       <c r="H116" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I116" t="n">
         <v>2</v>
@@ -12755,28 +12755,28 @@
         <v>150</v>
       </c>
       <c r="B117" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C117" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="D117" t="n">
-        <v>0.625</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="E117" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.742857142857143</v>
       </c>
       <c r="F117" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G117" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -12802,28 +12802,28 @@
         <v>150</v>
       </c>
       <c r="B118" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.7</v>
       </c>
       <c r="D118" t="n">
-        <v>0.9375</v>
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="F118" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G118" t="n">
         <v>120</v>
       </c>
       <c r="H118" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -12849,25 +12849,25 @@
         <v>150</v>
       </c>
       <c r="B119" t="n">
-        <v>0.7933333333333333</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C119" t="n">
-        <v>0.7454545454545455</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="D119" t="n">
-        <v>0.7068965517241379</v>
+        <v>0.7671232876712328</v>
       </c>
       <c r="E119" t="n">
-        <v>0.7256637168141592</v>
+        <v>0.8549618320610687</v>
       </c>
       <c r="F119" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G119" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H119" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I119" t="n">
         <v>17</v>
@@ -12896,28 +12896,28 @@
         <v>150</v>
       </c>
       <c r="B120" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.9066666666666666</v>
       </c>
       <c r="C120" t="n">
-        <v>0.726027397260274</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="D120" t="n">
-        <v>0.9137931034482759</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8091603053435115</v>
+        <v>0.9054054054054055</v>
       </c>
       <c r="F120" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="G120" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H120" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -12943,28 +12943,28 @@
         <v>150</v>
       </c>
       <c r="B121" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="C121" t="n">
-        <v>0.8771929824561403</v>
+        <v>0.9104477611940298</v>
       </c>
       <c r="D121" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8356164383561644</v>
       </c>
       <c r="E121" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.8714285714285713</v>
       </c>
       <c r="F121" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G121" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="H121" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I121" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -12990,28 +12990,28 @@
         <v>150</v>
       </c>
       <c r="B122" t="n">
-        <v>0.6933333333333334</v>
+        <v>0.78</v>
       </c>
       <c r="C122" t="n">
-        <v>0.581081081081081</v>
+        <v>0.7702702702702703</v>
       </c>
       <c r="D122" t="n">
-        <v>0.7413793103448276</v>
+        <v>0.7808219178082192</v>
       </c>
       <c r="E122" t="n">
-        <v>0.6515151515151516</v>
+        <v>0.7755102040816327</v>
       </c>
       <c r="F122" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G122" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H122" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I122" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -13037,28 +13037,28 @@
         <v>150</v>
       </c>
       <c r="B123" t="n">
-        <v>0.7933333333333333</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="C123" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.9811320754716981</v>
       </c>
       <c r="D123" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.7123287671232876</v>
       </c>
       <c r="E123" t="n">
-        <v>0.7207207207207208</v>
+        <v>0.8253968253968254</v>
       </c>
       <c r="F123" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G123" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H123" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -13084,28 +13084,28 @@
         <v>150</v>
       </c>
       <c r="B124" t="n">
-        <v>0.8</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="C124" t="n">
-        <v>0.7</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="D124" t="n">
-        <v>0.8448275862068966</v>
+        <v>0.8493150684931506</v>
       </c>
       <c r="E124" t="n">
-        <v>0.765625</v>
+        <v>0.8671328671328671</v>
       </c>
       <c r="F124" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G124" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H124" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I124" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -13131,28 +13131,28 @@
         <v>150</v>
       </c>
       <c r="B125" t="n">
-        <v>0.7266666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="C125" t="n">
-        <v>0.6197183098591549</v>
+        <v>0.7605633802816901</v>
       </c>
       <c r="D125" t="n">
-        <v>0.7586206896551724</v>
+        <v>0.7397260273972602</v>
       </c>
       <c r="E125" t="n">
-        <v>0.6821705426356589</v>
+        <v>0.75</v>
       </c>
       <c r="F125" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G125" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H125" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I125" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -13178,28 +13178,28 @@
         <v>150</v>
       </c>
       <c r="B126" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="C126" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D126" t="n">
-        <v>0.6724137931034483</v>
+        <v>0.6575342465753424</v>
       </c>
       <c r="E126" t="n">
-        <v>0.6964285714285714</v>
+        <v>0.7559055118110236</v>
       </c>
       <c r="F126" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G126" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H126" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I126" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -13225,28 +13225,28 @@
         <v>150</v>
       </c>
       <c r="B127" t="n">
-        <v>0.6066666666666667</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="C127" t="n">
-        <v>0.4952380952380953</v>
+        <v>0.6513761467889908</v>
       </c>
       <c r="D127" t="n">
-        <v>0.896551724137931</v>
+        <v>0.9726027397260274</v>
       </c>
       <c r="E127" t="n">
-        <v>0.6380368098159509</v>
+        <v>0.7802197802197802</v>
       </c>
       <c r="F127" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G127" t="n">
         <v>39</v>
       </c>
       <c r="H127" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="I127" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -13272,19 +13272,19 @@
         <v>150</v>
       </c>
       <c r="B128" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6733333333333333</v>
       </c>
       <c r="C128" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="D128" t="n">
-        <v>0.5074626865671642</v>
+        <v>0.746268656716418</v>
       </c>
       <c r="E128" t="n">
-        <v>0.5112781954887218</v>
+        <v>0.6711409395973154</v>
       </c>
       <c r="F128" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G128" t="n">
         <v>51</v>
@@ -13293,7 +13293,7 @@
         <v>32</v>
       </c>
       <c r="I128" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -13319,28 +13319,28 @@
         <v>150</v>
       </c>
       <c r="B129" t="n">
-        <v>0.7133333333333334</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="C129" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8142857142857143</v>
       </c>
       <c r="D129" t="n">
-        <v>0.5970149253731343</v>
+        <v>0.8507462686567164</v>
       </c>
       <c r="E129" t="n">
-        <v>0.6504065040650405</v>
+        <v>0.832116788321168</v>
       </c>
       <c r="F129" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G129" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H129" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I129" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -13366,19 +13366,19 @@
         <v>150</v>
       </c>
       <c r="B130" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="C130" t="n">
-        <v>0.734375</v>
+        <v>0.7068965517241379</v>
       </c>
       <c r="D130" t="n">
-        <v>0.7014925373134329</v>
+        <v>0.6119402985074627</v>
       </c>
       <c r="E130" t="n">
-        <v>0.7175572519083969</v>
+        <v>0.6559999999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G130" t="n">
         <v>66</v>
@@ -13387,7 +13387,7 @@
         <v>17</v>
       </c>
       <c r="I130" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -13413,19 +13413,19 @@
         <v>150</v>
       </c>
       <c r="B131" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="C131" t="n">
-        <v>0.3883495145631068</v>
+        <v>0.4793388429752066</v>
       </c>
       <c r="D131" t="n">
-        <v>0.5970149253731343</v>
+        <v>0.8656716417910447</v>
       </c>
       <c r="E131" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.6170212765957447</v>
       </c>
       <c r="F131" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G131" t="n">
         <v>20</v>
@@ -13434,7 +13434,7 @@
         <v>63</v>
       </c>
       <c r="I131" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -13460,19 +13460,19 @@
         <v>150</v>
       </c>
       <c r="B132" t="n">
-        <v>0.62</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="C132" t="n">
-        <v>0.65625</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="D132" t="n">
-        <v>0.3134328358208955</v>
+        <v>0.5522388059701493</v>
       </c>
       <c r="E132" t="n">
-        <v>0.4242424242424243</v>
+        <v>0.6434782608695653</v>
       </c>
       <c r="F132" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G132" t="n">
         <v>72</v>
@@ -13481,7 +13481,7 @@
         <v>11</v>
       </c>
       <c r="I132" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -13507,19 +13507,19 @@
         <v>150</v>
       </c>
       <c r="B133" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="C133" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="D133" t="n">
-        <v>0.5223880597014925</v>
+        <v>0.7014925373134329</v>
       </c>
       <c r="E133" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.7401574803149608</v>
       </c>
       <c r="F133" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G133" t="n">
         <v>70</v>
@@ -13528,7 +13528,7 @@
         <v>13</v>
       </c>
       <c r="I133" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -13554,19 +13554,19 @@
         <v>150</v>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="C134" t="n">
-        <v>0.4393939393939394</v>
+        <v>0.5542168674698795</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4328358208955224</v>
+        <v>0.6865671641791045</v>
       </c>
       <c r="E134" t="n">
-        <v>0.4360902255639098</v>
+        <v>0.6133333333333333</v>
       </c>
       <c r="F134" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="G134" t="n">
         <v>46</v>
@@ -13575,7 +13575,7 @@
         <v>37</v>
       </c>
       <c r="I134" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -13601,19 +13601,19 @@
         <v>150</v>
       </c>
       <c r="B135" t="n">
-        <v>0.5933333333333334</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="C135" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="D135" t="n">
-        <v>0.2985074626865671</v>
+        <v>0.5671641791044776</v>
       </c>
       <c r="E135" t="n">
-        <v>0.396039603960396</v>
+        <v>0.6386554621848739</v>
       </c>
       <c r="F135" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="G135" t="n">
         <v>69</v>
@@ -13622,7 +13622,7 @@
         <v>14</v>
       </c>
       <c r="I135" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -13648,19 +13648,19 @@
         <v>150</v>
       </c>
       <c r="B136" t="n">
-        <v>0.5266666666666666</v>
+        <v>0.6266666666666667</v>
       </c>
       <c r="C136" t="n">
-        <v>0.4743589743589743</v>
+        <v>0.5591397849462365</v>
       </c>
       <c r="D136" t="n">
-        <v>0.5522388059701493</v>
+        <v>0.7761194029850746</v>
       </c>
       <c r="E136" t="n">
-        <v>0.5103448275862068</v>
+        <v>0.65</v>
       </c>
       <c r="F136" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G136" t="n">
         <v>42</v>
@@ -13669,7 +13669,7 @@
         <v>41</v>
       </c>
       <c r="I136" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -13695,28 +13695,28 @@
         <v>150</v>
       </c>
       <c r="B137" t="n">
-        <v>0.6066666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C137" t="n">
-        <v>0.5098039215686274</v>
+        <v>0.5</v>
       </c>
       <c r="D137" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.5272727272727272</v>
       </c>
       <c r="E137" t="n">
-        <v>0.4684684684684685</v>
+        <v>0.5132743362831858</v>
       </c>
       <c r="F137" t="n">
+        <v>29</v>
+      </c>
+      <c r="G137" t="n">
+        <v>66</v>
+      </c>
+      <c r="H137" t="n">
+        <v>29</v>
+      </c>
+      <c r="I137" t="n">
         <v>26</v>
-      </c>
-      <c r="G137" t="n">
-        <v>65</v>
-      </c>
-      <c r="H137" t="n">
-        <v>25</v>
-      </c>
-      <c r="I137" t="n">
-        <v>34</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -13742,28 +13742,28 @@
         <v>150</v>
       </c>
       <c r="B138" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="C138" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.711864406779661</v>
       </c>
       <c r="D138" t="n">
-        <v>0.6</v>
+        <v>0.7636363636363637</v>
       </c>
       <c r="E138" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.736842105263158</v>
       </c>
       <c r="F138" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G138" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H138" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I138" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -13789,28 +13789,28 @@
         <v>150</v>
       </c>
       <c r="B139" t="n">
-        <v>0.66</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="C139" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3090909090909091</v>
       </c>
       <c r="E139" t="n">
-        <v>0.4950495049504951</v>
+        <v>0.3820224719101123</v>
       </c>
       <c r="F139" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="G139" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H139" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I139" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -13836,28 +13836,28 @@
         <v>150</v>
       </c>
       <c r="B140" t="n">
-        <v>0.34</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="D140" t="n">
-        <v>0.45</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3529411764705882</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="F140" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G140" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H140" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I140" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -13883,28 +13883,28 @@
         <v>150</v>
       </c>
       <c r="B141" t="n">
-        <v>0.62</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="C141" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2</v>
+        <v>0.3818181818181818</v>
       </c>
       <c r="E141" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.4772727272727273</v>
       </c>
       <c r="F141" t="n">
+        <v>21</v>
+      </c>
+      <c r="G141" t="n">
+        <v>83</v>
+      </c>
+      <c r="H141" t="n">
         <v>12</v>
       </c>
-      <c r="G141" t="n">
-        <v>81</v>
-      </c>
-      <c r="H141" t="n">
-        <v>9</v>
-      </c>
       <c r="I141" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -13930,28 +13930,28 @@
         <v>150</v>
       </c>
       <c r="B142" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.72</v>
       </c>
       <c r="C142" t="n">
-        <v>0.65625</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="D142" t="n">
-        <v>0.35</v>
+        <v>0.4909090909090909</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4565217391304347</v>
+        <v>0.5625</v>
       </c>
       <c r="F142" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G142" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H142" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I142" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -13977,28 +13977,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.5466666666666666</v>
       </c>
       <c r="C143" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="D143" t="n">
-        <v>0.3166666666666667</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="E143" t="n">
-        <v>0.3247863247863248</v>
+        <v>0.46875</v>
       </c>
       <c r="F143" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G143" t="n">
         <v>52</v>
       </c>
       <c r="H143" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I143" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -14024,28 +14024,28 @@
         <v>150</v>
       </c>
       <c r="B144" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C144" t="n">
-        <v>0.4375</v>
+        <v>0.5757575757575758</v>
       </c>
       <c r="D144" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.3454545454545455</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1842105263157895</v>
+        <v>0.4318181818181818</v>
       </c>
       <c r="F144" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G144" t="n">
         <v>81</v>
       </c>
       <c r="H144" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I144" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -14071,28 +14071,28 @@
         <v>150</v>
       </c>
       <c r="B145" t="n">
-        <v>0.52</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="C145" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="D145" t="n">
-        <v>0.35</v>
+        <v>0.4727272727272727</v>
       </c>
       <c r="E145" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F145" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G145" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H145" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I145" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
